--- a/fotogramas.xlsx
+++ b/fotogramas.xlsx
@@ -5,11 +5,19 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="F0" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="F1" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="F2" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="F3" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="F4" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="F5" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="F6" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="F7" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="F8" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="F9" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="22">
   <si>
     <t xml:space="preserve">CAPA</t>
   </si>
@@ -71,10 +79,22 @@
     <t xml:space="preserve">Y</t>
   </si>
   <si>
-    <t xml:space="preserve">RayoAmarillo</t>
+    <t xml:space="preserve">#FFBB66</t>
   </si>
   <si>
-    <t xml:space="preserve">#FFD93D</t>
+    <t xml:space="preserve">EXPLOCION 02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPLOCION 03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPLOCION 04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#777799</t>
   </si>
 </sst>
 </file>
@@ -84,7 +104,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -112,6 +132,11 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -162,7 +187,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -185,6 +210,14 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -409,8 +442,8 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="str">
-        <f aca="false">D1</f>
-        <v>#FFFFDD</v>
+        <f aca="false">D2</f>
+        <v>#FFFF88</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>9</v>
@@ -1045,6 +1078,131 @@
       </c>
       <c r="B81" s="5" t="n">
         <v>-824.27</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Página &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="16.92"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="str">
+        <f aca="false">D5</f>
+        <v>#777799</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
+        <v>-565.96</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>-1266.52</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
+        <v>-354.75</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>293.58</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
+        <v>1433.46</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>330.19</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
+        <v>1447.54</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>-1314.4</v>
       </c>
     </row>
   </sheetData>
@@ -1063,7 +1221,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="16.39"/>
@@ -1074,7 +1232,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1084,13 +1248,26 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>17</v>
+      <c r="B3" s="1" t="str">
+        <f aca="false">D4</f>
+        <v>#AA5555</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1100,6 +1277,12 @@
       <c r="B4" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
@@ -1107,6 +1290,7397 @@
       </c>
       <c r="B5" s="1" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
+        <v>712.57</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>-520.45</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
+        <v>711.39</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>-318.38</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
+        <v>675.95</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>-447.75</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="n">
+        <v>743.88</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>-435.34</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="n">
+        <v>715.52</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>-496.18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="n">
+        <v>907.5</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>-423.53</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="n">
+        <v>839.57</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>-503.27</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
+        <v>758.64</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>-545.8</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="n">
+        <v>866.71</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>-619.5</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="n">
+        <v>820.28</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>-637.24</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="n">
+        <v>736.12</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>-624.98</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="n">
+        <v>800</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>-800</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="n">
+        <v>627.51</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>-618.14</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="n">
+        <v>691.24</v>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>-667.48</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="n">
+        <v>575.09</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>-840.16</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="n">
+        <v>600.78</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>-648.97</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="n">
+        <v>486.69</v>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>-780.55</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="n">
+        <v>591.53</v>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>-577.02</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="n">
+        <v>506.22</v>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>-633.56</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="n">
+        <v>538.08</v>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>-559.55</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="n">
+        <v>492.85</v>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>-535.9</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="n">
+        <v>550.42</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>-528.71</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="n">
+        <v>481.55</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>-485.54</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="n">
+        <v>540.14</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>-489.65</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="n">
+        <v>496.97</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>-438.25</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="n">
+        <v>554.53</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>-450.59</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="n">
+        <v>478.46</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>-347.8</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="n">
+        <v>600.78</v>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>-434.14</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Página &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D48"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="18.2"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="str">
+        <f aca="false">D4</f>
+        <v>#AA5555</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
+        <v>554.96</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>-457.84</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
+        <v>688.87</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>-257.93</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
+        <v>848.23</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>-136.29</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
+        <v>686.04</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>-339.03</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="n">
+        <v>787.88</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>-251.33</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="n">
+        <v>700.18</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>-373.92</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="n">
+        <v>660.58</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>-451.24</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="n">
+        <v>709.61</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>-470.1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
+        <v>975.53</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>-333.37</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="n">
+        <v>875.57</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>-420.12</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="n">
+        <v>1017.02</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>-357.89</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="n">
+        <v>821.82</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>-522.9</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="n">
+        <v>966.1</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>-578.54</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="n">
+        <v>918.95</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>-606.83</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="n">
+        <v>990.61</v>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>-620.97</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="n">
+        <v>831.25</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>-672.83</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="n">
+        <v>893.49</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>-719.98</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="n">
+        <v>822.77</v>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>-719.04</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="n">
+        <v>882.17</v>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>-753.93</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="n">
+        <v>800</v>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>-750</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="n">
+        <v>856.71</v>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>-773.73</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="n">
+        <v>795.42</v>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>-771.85</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="n">
+        <v>840.68</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>-823.71</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="n">
+        <v>604</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>-771.85</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="n">
+        <v>650</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="n">
+        <v>529.5</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>-874.63</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="n">
+        <v>545.54</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>-736.01</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="n">
+        <v>449.35</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>-814.28</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="n">
+        <v>507.82</v>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>-728.47</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="n">
+        <v>376.75</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>-818.99</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="n">
+        <v>464.44</v>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>-707.72</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="n">
+        <v>541.76</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>-682.26</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="n">
+        <v>373.92</v>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>-731.3</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="n">
+        <v>454.07</v>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>-671.89</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="n">
+        <v>354.11</v>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>-682.26</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="n">
+        <v>416.35</v>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>-640.77</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="n">
+        <v>357.89</v>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>-625.69</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="n">
+        <v>482.36</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>-620.97</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="n">
+        <v>482.36</v>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>-541.76</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="n">
+        <v>529.5</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>-626.63</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="n">
+        <v>389.95</v>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>-256.05</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="n">
+        <v>494.62</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>-429.55</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4" t="n">
+        <v>494.62</v>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>-357.89</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Página &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D194"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="17.15"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="str">
+        <f aca="false">D4</f>
+        <v>#AA5555</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
+        <v>428.26</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>-227.89</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
+        <v>412.58</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>-92.64</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
+        <v>442.33</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>-149.99</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
+        <v>452.07</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>-122.39</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="n">
+        <v>434.22</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>-19.06</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="n">
+        <v>464.51</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>-90.47</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="n">
+        <v>432.05</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>114.03</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="n">
+        <v>483.99</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>-20.14</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
+        <v>509.42</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>-186.77</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="n">
+        <v>626.82</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>-24.47</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="n">
+        <v>580.83</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>-184.07</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="n">
+        <v>650</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="n">
+        <v>650</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>-150</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="n">
+        <v>625.73</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>-203</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="n">
+        <v>793.99</v>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>-74.79</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="n">
+        <v>773.43</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>-118.61</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="n">
+        <v>838.89</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>-74.24</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="n">
+        <v>750.17</v>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>-220.86</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="n">
+        <v>759.36</v>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>-294.44</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="n">
+        <v>1026.71</v>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>-182.51</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="n">
+        <v>879.86</v>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>-251.51</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="n">
+        <v>1036.44</v>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>-201.97</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="n">
+        <v>995.75</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>-254.16</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="n">
+        <v>809.53</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>-380.22</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="n">
+        <v>871.55</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>-378.29</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="n">
+        <v>841.37</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>-403.19</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="n">
+        <v>880.66</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>-405.37</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="n">
+        <v>856.96</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>-422.84</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="n">
+        <v>928.06</v>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>-413.48</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="n">
+        <v>862.26</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>-449.66</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="n">
+        <v>940.23</v>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>-472.42</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="n">
+        <v>872.24</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>-487.39</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="n">
+        <v>894.5</v>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>-497.25</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="n">
+        <v>931.99</v>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>-542.57</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="n">
+        <v>1016.46</v>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>-559.07</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="n">
+        <v>966.39</v>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>-577.81</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="n">
+        <v>944.29</v>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>-563.83</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="n">
+        <v>1050.87</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>-619.21</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="n">
+        <v>804.47</v>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>-602.75</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="n">
+        <v>936.12</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>-768.93</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="n">
+        <v>770.93</v>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>-722.9</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="n">
+        <v>854.51</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>-731.6</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4" t="n">
+        <v>775.86</v>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>-787.89</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4" t="n">
+        <v>707.5</v>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>-790.94</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4" t="n">
+        <v>696.43</v>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>-758.1</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="n">
+        <v>696.05</v>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>-792.47</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="n">
+        <v>660</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>-760</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="n">
+        <v>600</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>-960</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="n">
+        <v>605.87</v>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>-865.63</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="n">
+        <v>587.98</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>-942.28</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="n">
+        <v>580</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>-860</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="n">
+        <v>573.38</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>-906.15</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="n">
+        <v>556.96</v>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>-804.67</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4" t="n">
+        <v>558.05</v>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>-893.37</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="n">
+        <v>536.15</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>-791.9</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="n">
+        <v>380.68</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>-927.24</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4" t="n">
+        <v>435.62</v>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>-820.99</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="4" t="n">
+        <v>380</v>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>-860</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4" t="n">
+        <v>429.43</v>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>-785.66</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4" t="n">
+        <v>403.3</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>-820.37</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="4" t="n">
+        <v>304.51</v>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>-845.8</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="4" t="n">
+        <v>344.75</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>-812.65</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="4" t="n">
+        <v>268.65</v>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>-858.94</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="4" t="n">
+        <v>361.84</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>-748.65</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="4" t="n">
+        <v>245.48</v>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>-777.15</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="4" t="n">
+        <v>285.43</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>-735.67</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="4" t="n">
+        <v>200.55</v>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>-763.2</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="4" t="n">
+        <v>257.52</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>-703.75</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>-687.88</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="n">
+        <v>283.33</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>-642.58</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="4" t="n">
+        <v>276.56</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>-612.16</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="4" t="n">
+        <v>156.41</v>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>-488.99</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4" t="n">
+        <v>257.49</v>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>-535.29</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4" t="n">
+        <v>171.54</v>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>-458.43</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="4" t="n">
+        <v>241.45</v>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>-492.32</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="4" t="n">
+        <v>196.06</v>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>-455.4</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="4" t="n">
+        <v>268.08</v>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>-469.02</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="4" t="n">
+        <v>284.1</v>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>-448.34</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="4" t="n">
+        <v>217.32</v>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>-352.61</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="4" t="n">
+        <v>296.01</v>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>-412.08</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>-360</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="4" t="n">
+        <v>319.18</v>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>-391.95</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="4" t="n">
+        <v>288.99</v>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>-359.32</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="4" t="n">
+        <v>338.4</v>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>-365.42</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="4" t="n">
+        <v>243.7</v>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>-190.19</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="4" t="n">
+        <v>330.02</v>
+      </c>
+      <c r="B91" s="5" t="n">
+        <v>-298.88</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="4" t="n">
+        <v>319.15</v>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>-254.12</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="4" t="n">
+        <v>352.07</v>
+      </c>
+      <c r="B93" s="5" t="n">
+        <v>-301.12</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="4" t="n">
+        <v>304.44</v>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>-184.11</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="4" t="n">
+        <v>385</v>
+      </c>
+      <c r="B95" s="5" t="n">
+        <v>-250.61</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="4" t="n">
+        <v>374.13</v>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>-215.76</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="4" t="n">
+        <v>410.89</v>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>-238.14</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B100" s="1" t="str">
+        <f aca="false">D3</f>
+        <v>#FFBB66</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B101" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="4" t="n">
+        <v>529.39</v>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>-235.58</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="4" t="n">
+        <v>583.48</v>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>-220.13</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="4" t="n">
+        <v>600</v>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>-250</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="4" t="n">
+        <v>678.79</v>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>-191.28</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="4" t="n">
+        <v>619.55</v>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>-278.34</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="4" t="n">
+        <v>877.13</v>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>-166.55</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="4" t="n">
+        <v>643.76</v>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>-287.61</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="4" t="n">
+        <v>746.79</v>
+      </c>
+      <c r="B110" s="5" t="n">
+        <v>-288.64</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="4" t="n">
+        <v>733.91</v>
+      </c>
+      <c r="B111" s="5" t="n">
+        <v>-330.89</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="4" t="n">
+        <v>746.79</v>
+      </c>
+      <c r="B112" s="5" t="n">
+        <v>-372.1</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="4" t="n">
+        <v>808.09</v>
+      </c>
+      <c r="B113" s="5" t="n">
+        <v>-355.1</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="4" t="n">
+        <v>747.31</v>
+      </c>
+      <c r="B114" s="5" t="n">
+        <v>-424.13</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="4" t="n">
+        <v>798.82</v>
+      </c>
+      <c r="B115" s="5" t="n">
+        <v>-456.59</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="4" t="n">
+        <v>751.94</v>
+      </c>
+      <c r="B116" s="5" t="n">
+        <v>-470.5</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="4" t="n">
+        <v>862.7</v>
+      </c>
+      <c r="B117" s="5" t="n">
+        <v>-550.35</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="4" t="n">
+        <v>752.46</v>
+      </c>
+      <c r="B118" s="5" t="n">
+        <v>-526.13</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="4" t="n">
+        <v>775.31</v>
+      </c>
+      <c r="B119" s="5" t="n">
+        <v>-618.86</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="4" t="n">
+        <v>669.92</v>
+      </c>
+      <c r="B120" s="5" t="n">
+        <v>-617.78</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="4" t="n">
+        <v>700</v>
+      </c>
+      <c r="B121" s="5" t="n">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="4" t="n">
+        <v>628.27</v>
+      </c>
+      <c r="B122" s="5" t="n">
+        <v>-681.16</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="4" t="n">
+        <v>561.27</v>
+      </c>
+      <c r="B123" s="5" t="n">
+        <v>-674.28</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="4" t="n">
+        <v>475.21</v>
+      </c>
+      <c r="B124" s="5" t="n">
+        <v>-746.76</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="4" t="n">
+        <v>465.77</v>
+      </c>
+      <c r="B125" s="5" t="n">
+        <v>-683.57</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="B126" s="5" t="n">
+        <v>-720</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="4" t="n">
+        <v>438.69</v>
+      </c>
+      <c r="B127" s="5" t="n">
+        <v>-665.11</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="4" t="n">
+        <v>385.34</v>
+      </c>
+      <c r="B128" s="5" t="n">
+        <v>-711.48</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="4" t="n">
+        <v>440</v>
+      </c>
+      <c r="B129" s="5" t="n">
+        <v>-620</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="4" t="n">
+        <v>359.9</v>
+      </c>
+      <c r="B130" s="5" t="n">
+        <v>-647.46</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="4" t="n">
+        <v>437.04</v>
+      </c>
+      <c r="B131" s="5" t="n">
+        <v>-595.35</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="4" t="n">
+        <v>370.57</v>
+      </c>
+      <c r="B132" s="5" t="n">
+        <v>-593.3</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="4" t="n">
+        <v>195.35</v>
+      </c>
+      <c r="B133" s="5" t="n">
+        <v>-642.15</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="4" t="n">
+        <v>361.68</v>
+      </c>
+      <c r="B134" s="5" t="n">
+        <v>-517.4</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="4" t="n">
+        <v>312.54</v>
+      </c>
+      <c r="B135" s="5" t="n">
+        <v>-499.58</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="4" t="n">
+        <v>348.18</v>
+      </c>
+      <c r="B136" s="5" t="n">
+        <v>-469.88</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="4" t="n">
+        <v>353.58</v>
+      </c>
+      <c r="B137" s="5" t="n">
+        <v>-392.65</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="4" t="n">
+        <v>409.75</v>
+      </c>
+      <c r="B138" s="5" t="n">
+        <v>-425.05</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="4" t="n">
+        <v>363.3</v>
+      </c>
+      <c r="B139" s="5" t="n">
+        <v>-304.62</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="4" t="n">
+        <v>410.83</v>
+      </c>
+      <c r="B140" s="5" t="n">
+        <v>-325.14</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="4" t="n">
+        <v>404.89</v>
+      </c>
+      <c r="B141" s="5" t="n">
+        <v>-263.58</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="4" t="n">
+        <v>442.69</v>
+      </c>
+      <c r="B142" s="5" t="n">
+        <v>-326.22</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="4" t="n">
+        <v>464.03</v>
+      </c>
+      <c r="B143" s="5" t="n">
+        <v>-212.52</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B146" s="1" t="str">
+        <f aca="false">D2</f>
+        <v>#FFFF88</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B147" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="4" t="n">
+        <v>496.09</v>
+      </c>
+      <c r="B149" s="5" t="n">
+        <v>-371.94</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B150" s="5" t="n">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="4" t="n">
+        <v>540.53</v>
+      </c>
+      <c r="B151" s="5" t="n">
+        <v>-368.24</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="4" t="n">
+        <v>624.66</v>
+      </c>
+      <c r="B152" s="5" t="n">
+        <v>-340.2</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="4" t="n">
+        <v>606.14</v>
+      </c>
+      <c r="B153" s="5" t="n">
+        <v>-380.41</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="4" t="n">
+        <v>699.26</v>
+      </c>
+      <c r="B154" s="5" t="n">
+        <v>-413.74</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="4" t="n">
+        <v>652.17</v>
+      </c>
+      <c r="B155" s="5" t="n">
+        <v>-460.83</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="4" t="n">
+        <v>690.79</v>
+      </c>
+      <c r="B156" s="5" t="n">
+        <v>-501.57</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="4" t="n">
+        <v>623.6</v>
+      </c>
+      <c r="B157" s="5" t="n">
+        <v>-512.15</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="4" t="n">
+        <v>659.05</v>
+      </c>
+      <c r="B158" s="5" t="n">
+        <v>-561.35</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="4" t="n">
+        <v>616.72</v>
+      </c>
+      <c r="B159" s="5" t="n">
+        <v>-559.24</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="4" t="n">
+        <v>584.45</v>
+      </c>
+      <c r="B160" s="5" t="n">
+        <v>-590.45</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="4" t="n">
+        <v>497.68</v>
+      </c>
+      <c r="B161" s="5" t="n">
+        <v>-609.5</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="4" t="n">
+        <v>511.96</v>
+      </c>
+      <c r="B162" s="5" t="n">
+        <v>-550.77</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="4" t="n">
+        <v>450</v>
+      </c>
+      <c r="B163" s="5" t="n">
+        <v>-550</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="4" t="n">
+        <v>493.45</v>
+      </c>
+      <c r="B164" s="5" t="n">
+        <v>-512.15</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="4" t="n">
+        <v>420.96</v>
+      </c>
+      <c r="B165" s="5" t="n">
+        <v>-477.23</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="4" t="n">
+        <v>480.22</v>
+      </c>
+      <c r="B166" s="5" t="n">
+        <v>-426.44</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="4" t="n">
+        <v>419.38</v>
+      </c>
+      <c r="B167" s="5" t="n">
+        <v>-356.07</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="4" t="n">
+        <v>507.2</v>
+      </c>
+      <c r="B168" s="5" t="n">
+        <v>-405.8</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B171" s="1" t="str">
+        <f aca="false">D1</f>
+        <v>#FFFFDD</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B172" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="4" t="n">
+        <v>493.23</v>
+      </c>
+      <c r="B174" s="5" t="n">
+        <v>-433.48</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="4" t="n">
+        <v>535.87</v>
+      </c>
+      <c r="B175" s="5" t="n">
+        <v>-378.86</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="4" t="n">
+        <v>552.15</v>
+      </c>
+      <c r="B176" s="5" t="n">
+        <v>-425.81</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="4" t="n">
+        <v>607.25</v>
+      </c>
+      <c r="B177" s="5" t="n">
+        <v>-414.79</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="4" t="n">
+        <v>600</v>
+      </c>
+      <c r="B178" s="5" t="n">
+        <v>-440</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="4" t="n">
+        <v>643.66</v>
+      </c>
+      <c r="B179" s="5" t="n">
+        <v>-435.87</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="4" t="n">
+        <v>625.93</v>
+      </c>
+      <c r="B180" s="5" t="n">
+        <v>-469.41</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="4" t="n">
+        <v>637.43</v>
+      </c>
+      <c r="B181" s="5" t="n">
+        <v>-492.4</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="4" t="n">
+        <v>586.17</v>
+      </c>
+      <c r="B182" s="5" t="n">
+        <v>-490.01</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="4" t="n">
+        <v>640</v>
+      </c>
+      <c r="B183" s="5" t="n">
+        <v>-560</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="4" t="n">
+        <v>561.74</v>
+      </c>
+      <c r="B184" s="5" t="n">
+        <v>-527.86</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="4" t="n">
+        <v>595.75</v>
+      </c>
+      <c r="B185" s="5" t="n">
+        <v>-587.74</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="4" t="n">
+        <v>546.88</v>
+      </c>
+      <c r="B186" s="5" t="n">
+        <v>-543.19</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="4" t="n">
+        <v>516.7</v>
+      </c>
+      <c r="B187" s="5" t="n">
+        <v>-570.49</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="4" t="n">
+        <v>529.16</v>
+      </c>
+      <c r="B188" s="5" t="n">
+        <v>-522.59</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="4" t="n">
+        <v>464.48</v>
+      </c>
+      <c r="B189" s="5" t="n">
+        <v>-574.8</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="4" t="n">
+        <v>485.56</v>
+      </c>
+      <c r="B190" s="5" t="n">
+        <v>-524.5</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="4" t="n">
+        <v>462.57</v>
+      </c>
+      <c r="B191" s="5" t="n">
+        <v>-512.05</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="4" t="n">
+        <v>492.75</v>
+      </c>
+      <c r="B192" s="5" t="n">
+        <v>-490.01</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="4" t="n">
+        <v>458.73</v>
+      </c>
+      <c r="B193" s="5" t="n">
+        <v>-443.06</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="4" t="n">
+        <v>500.89</v>
+      </c>
+      <c r="B194" s="5" t="n">
+        <v>-453.12</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Página &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D197"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="17.5"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="str">
+        <f aca="false">D4</f>
+        <v>#AA5555</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
+        <v>466.82</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>-108.16</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
+        <v>775.55</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>391.21</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
+        <v>671.95</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>100.09</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
+        <v>590.1</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>-122.66</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="n">
+        <v>1032.49</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>77.29</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="n">
+        <v>803.53</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>-115.41</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="n">
+        <v>980.69</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>-30.45</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="n">
+        <v>813.89</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>-155.81</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="n">
+        <v>841.63</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>-239.3</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="n">
+        <v>984.48</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>-220.47</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="n">
+        <v>924.68</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>-279.17</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="n">
+        <v>1039.86</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>-258.13</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="n">
+        <v>899.21</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>-322.36</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="n">
+        <v>1068.65</v>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>-374.41</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="n">
+        <v>825.48</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>-419.5</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="n">
+        <v>1009.92</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>-460.28</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="n">
+        <v>928.99</v>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>-489.14</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="n">
+        <v>1155.46</v>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>-664.16</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="n">
+        <v>849.95</v>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>-522.38</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="n">
+        <v>906.41</v>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>-516.74</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="n">
+        <v>1016.82</v>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>-784.61</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="n">
+        <v>858.71</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>-705.95</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="n">
+        <v>900.83</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>-674.25</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="n">
+        <v>1076.37</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>-1026.56</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="n">
+        <v>746.34</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>-720.18</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="n">
+        <v>876.44</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>-945.67</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="n">
+        <v>900.83</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>-674.25</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="n">
+        <v>1076.37</v>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>-1026.56</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="n">
+        <v>746.34</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>-720.18</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="n">
+        <v>876.44</v>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>-945.67</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="n">
+        <v>754.4</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>-824.32</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="n">
+        <v>838.78</v>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>-1036.34</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="n">
+        <v>700</v>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>-800</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="n">
+        <v>739.72</v>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>-826.93</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="n">
+        <v>729.9</v>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>-1009.39</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="n">
+        <v>633.76</v>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>-904.98</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="n">
+        <v>659.48</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>-980.63</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="n">
+        <v>578.18</v>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>-931.54</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="n">
+        <v>550</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>-850</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="n">
+        <v>519.89</v>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>-822.63</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="n">
+        <v>419.44</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>-963.26</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4" t="n">
+        <v>441.11</v>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>-851.92</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4" t="n">
+        <v>462.77</v>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>-861.88</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4" t="n">
+        <v>306.8</v>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>-1011.35</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="n">
+        <v>290.77</v>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>-935.53</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="n">
+        <v>147.08</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>-994.12</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="n">
+        <v>250.87</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>-813.58</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="n">
+        <v>119.09</v>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>-890.45</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="n">
+        <v>210.39</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>-701.56</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="n">
+        <v>199.84</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>-665.85</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="n">
+        <v>110.53</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>-719.97</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="n">
+        <v>67.91</v>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>-723.36</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4" t="n">
+        <v>125.2</v>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>-610.88</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="n">
+        <v>179.77</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>-506.44</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="n">
+        <v>67.89</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>-441.09</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4" t="n">
+        <v>112.44</v>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>-381.69</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="4" t="n">
+        <v>66.9</v>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>-263.86</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4" t="n">
+        <v>143.14</v>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>-338.12</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4" t="n">
+        <v>93.63</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>-214.36</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="4" t="n">
+        <v>135.21</v>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>-247.03</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="4" t="n">
+        <v>61.95</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>-46.04</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="4" t="n">
+        <v>57.99</v>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>15.35</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="4" t="n">
+        <v>210.46</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>-155.94</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="4" t="n">
+        <v>174.82</v>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>-99.5</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="4" t="n">
+        <v>227.3</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>-118.31</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="4" t="n">
+        <v>264.92</v>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>-180.69</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="4" t="n">
+        <v>222.35</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>-66.83</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="n">
+        <v>309.48</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>-116.33</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="n">
+        <v>350</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="4" t="n">
+        <v>325.43</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>32.69</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="4" t="n">
+        <v>381.06</v>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>-35.03</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4" t="n">
+        <v>358.08</v>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>71.39</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4" t="n">
+        <v>408.88</v>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>-30.19</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="4" t="n">
+        <v>405.25</v>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>125.81</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="4" t="n">
+        <v>448.78</v>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>-44.7</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B84" s="1" t="str">
+        <f aca="false">D3</f>
+        <v>#FFBB66</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B85" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="4" t="n">
+        <v>550</v>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>-250</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="4" t="n">
+        <v>754.2</v>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>19.59</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="4" t="n">
+        <v>661.78</v>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>-219.92</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="4" t="n">
+        <v>767.87</v>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>-37.03</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="4" t="n">
+        <v>683.91</v>
+      </c>
+      <c r="B91" s="5" t="n">
+        <v>-204.3</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="4" t="n">
+        <v>739.88</v>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>-188.03</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="4" t="n">
+        <v>734.67</v>
+      </c>
+      <c r="B93" s="5" t="n">
+        <v>-255.07</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="4" t="n">
+        <v>787.39</v>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>-312.99</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="4" t="n">
+        <v>802.03</v>
+      </c>
+      <c r="B95" s="5" t="n">
+        <v>-370.63</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="4" t="n">
+        <v>1048.19</v>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>-374.17</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="4" t="n">
+        <v>796.62</v>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>-435.94</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="4" t="n">
+        <v>757.45</v>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>-481.88</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="4" t="n">
+        <v>800</v>
+      </c>
+      <c r="B99" s="5" t="n">
+        <v>-550</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="4" t="n">
+        <v>687.4</v>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>-576.78</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="4" t="n">
+        <v>742.39</v>
+      </c>
+      <c r="B101" s="5" t="n">
+        <v>-590.34</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="4" t="n">
+        <v>662.55</v>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>-594.11</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="4" t="n">
+        <v>678.37</v>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>-648.34</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="4" t="n">
+        <v>728.14</v>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>-685.43</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="4" t="n">
+        <v>670.84</v>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>-702.57</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="4" t="n">
+        <v>555.74</v>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>-733.91</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="4" t="n">
+        <v>489.42</v>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>-818.49</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="4" t="n">
+        <v>461.5</v>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>-742.15</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="4" t="n">
+        <v>327.05</v>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>-816.78</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="4" t="n">
+        <v>349.84</v>
+      </c>
+      <c r="B110" s="5" t="n">
+        <v>-686.89</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="4" t="n">
+        <v>254.7</v>
+      </c>
+      <c r="B111" s="5" t="n">
+        <v>-666.25</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="4" t="n">
+        <v>342.63</v>
+      </c>
+      <c r="B112" s="5" t="n">
+        <v>-489.31</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="4" t="n">
+        <v>225.84</v>
+      </c>
+      <c r="B113" s="5" t="n">
+        <v>-444.95</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="4" t="n">
+        <v>298.13</v>
+      </c>
+      <c r="B114" s="5" t="n">
+        <v>-388.71</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="4" t="n">
+        <v>205.19</v>
+      </c>
+      <c r="B115" s="5" t="n">
+        <v>-312.93</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="4" t="n">
+        <v>275.63</v>
+      </c>
+      <c r="B116" s="5" t="n">
+        <v>-293.4</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="4" t="n">
+        <v>296.94</v>
+      </c>
+      <c r="B117" s="5" t="n">
+        <v>-240.71</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="4" t="n">
+        <v>325.36</v>
+      </c>
+      <c r="B118" s="5" t="n">
+        <v>-260.25</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="4" t="n">
+        <v>337.2</v>
+      </c>
+      <c r="B119" s="5" t="n">
+        <v>-224.14</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="4" t="n">
+        <v>388.11</v>
+      </c>
+      <c r="B120" s="5" t="n">
+        <v>-259.66</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="4" t="n">
+        <v>408.23</v>
+      </c>
+      <c r="B121" s="5" t="n">
+        <v>-161.39</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="4" t="n">
+        <v>471.21</v>
+      </c>
+      <c r="B122" s="5" t="n">
+        <v>-188.32</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="4" t="n">
+        <v>514.74</v>
+      </c>
+      <c r="B123" s="5" t="n">
+        <v>-258.8</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B126" s="1" t="str">
+        <f aca="false">D2</f>
+        <v>#FFFF88</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B127" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="4" t="n">
+        <v>422.06</v>
+      </c>
+      <c r="B129" s="5" t="n">
+        <v>-341.05</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="4" t="n">
+        <v>384.86</v>
+      </c>
+      <c r="B130" s="5" t="n">
+        <v>-151.02</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="4" t="n">
+        <v>442.35</v>
+      </c>
+      <c r="B131" s="5" t="n">
+        <v>-213.23</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="4" t="n">
+        <v>428.82</v>
+      </c>
+      <c r="B132" s="5" t="n">
+        <v>-92.86</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="4" t="n">
+        <v>462.63</v>
+      </c>
+      <c r="B133" s="5" t="n">
+        <v>-251.78</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="4" t="n">
+        <v>464.66</v>
+      </c>
+      <c r="B134" s="5" t="n">
+        <v>-159.81</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="4" t="n">
+        <v>494.42</v>
+      </c>
+      <c r="B135" s="5" t="n">
+        <v>-186.73</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="4" t="n">
+        <v>591.13</v>
+      </c>
+      <c r="B136" s="5" t="n">
+        <v>-166.57</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="4" t="n">
+        <v>567.46</v>
+      </c>
+      <c r="B137" s="5" t="n">
+        <v>-268.01</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="4" t="n">
+        <v>678.36</v>
+      </c>
+      <c r="B138" s="5" t="n">
+        <v>-61.75</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="4" t="n">
+        <v>629</v>
+      </c>
+      <c r="B139" s="5" t="n">
+        <v>-249.75</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="4" t="n">
+        <v>637.79</v>
+      </c>
+      <c r="B140" s="5" t="n">
+        <v>-314</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="4" t="n">
+        <v>635.08</v>
+      </c>
+      <c r="B141" s="5" t="n">
+        <v>-352.54</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="4" t="n">
+        <v>821.73</v>
+      </c>
+      <c r="B142" s="5" t="n">
+        <v>-206.47</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="4" t="n">
+        <v>682.42</v>
+      </c>
+      <c r="B143" s="5" t="n">
+        <v>-417.47</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="4" t="n">
+        <v>783.19</v>
+      </c>
+      <c r="B144" s="5" t="n">
+        <v>-391.77</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="4" t="n">
+        <v>681.75</v>
+      </c>
+      <c r="B145" s="5" t="n">
+        <v>-452.63</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="4" t="n">
+        <v>767.63</v>
+      </c>
+      <c r="B146" s="5" t="n">
+        <v>-497.27</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="4" t="n">
+        <v>664.84</v>
+      </c>
+      <c r="B147" s="5" t="n">
+        <v>-526.35</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="4" t="n">
+        <v>637.11</v>
+      </c>
+      <c r="B148" s="5" t="n">
+        <v>-571.66</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="4" t="n">
+        <v>585.72</v>
+      </c>
+      <c r="B149" s="5" t="n">
+        <v>-554.07</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="4" t="n">
+        <v>678.36</v>
+      </c>
+      <c r="B150" s="5" t="n">
+        <v>-771.16</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="4" t="n">
+        <v>573.66</v>
+      </c>
+      <c r="B151" s="5" t="n">
+        <v>-646.9</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="4" t="n">
+        <v>515.04</v>
+      </c>
+      <c r="B152" s="5" t="n">
+        <v>-669.27</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="4" t="n">
+        <v>521.21</v>
+      </c>
+      <c r="B153" s="5" t="n">
+        <v>-592.9</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="4" t="n">
+        <v>341.47</v>
+      </c>
+      <c r="B154" s="5" t="n">
+        <v>-909.17</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="4" t="n">
+        <v>429.41</v>
+      </c>
+      <c r="B155" s="5" t="n">
+        <v>-669.27</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="4" t="n">
+        <v>434.04</v>
+      </c>
+      <c r="B156" s="5" t="n">
+        <v>-579.01</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="4" t="n">
+        <v>110.82</v>
+      </c>
+      <c r="B157" s="5" t="n">
+        <v>-899.14</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="4" t="n">
+        <v>349.96</v>
+      </c>
+      <c r="B158" s="5" t="n">
+        <v>-565.9</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="4" t="n">
+        <v>360.76</v>
+      </c>
+      <c r="B159" s="5" t="n">
+        <v>-511.13</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B160" s="5" t="n">
+        <v>-729.44</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="4" t="n">
+        <v>334.53</v>
+      </c>
+      <c r="B161" s="5" t="n">
+        <v>-474.1</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B162" s="5" t="n">
+        <v>-150</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="4" t="n">
+        <v>382.36</v>
+      </c>
+      <c r="B163" s="5" t="n">
+        <v>-435.53</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="4" t="n">
+        <v>350.73</v>
+      </c>
+      <c r="B164" s="5" t="n">
+        <v>-337.56</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D165" s="6"/>
+    </row>
+    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B167" s="1" t="str">
+        <f aca="false">D1</f>
+        <v>#FFFFDD</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B168" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B170" s="5" t="n">
+        <v>-350</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="4" t="n">
+        <v>542.01</v>
+      </c>
+      <c r="B171" s="5" t="n">
+        <v>-330.9</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="4" t="n">
+        <v>553.79</v>
+      </c>
+      <c r="B172" s="5" t="n">
+        <v>-372.13</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="4" t="n">
+        <v>623.88</v>
+      </c>
+      <c r="B173" s="5" t="n">
+        <v>-368.6</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="4" t="n">
+        <v>595.02</v>
+      </c>
+      <c r="B174" s="5" t="n">
+        <v>-407.47</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="4" t="n">
+        <v>1028.72</v>
+      </c>
+      <c r="B175" s="5" t="n">
+        <v>-68.18</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="4" t="n">
+        <v>623.45</v>
+      </c>
+      <c r="B176" s="5" t="n">
+        <v>-453.87</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="4" t="n">
+        <v>672.41</v>
+      </c>
+      <c r="B177" s="5" t="n">
+        <v>-519.6</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="4" t="n">
+        <v>581.39</v>
+      </c>
+      <c r="B178" s="5" t="n">
+        <v>-511.88</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="4" t="n">
+        <v>747.15</v>
+      </c>
+      <c r="B179" s="5" t="n">
+        <v>-912.72</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="4" t="n">
+        <v>655.02</v>
+      </c>
+      <c r="B180" s="5" t="n">
+        <v>-820.25</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="4" t="n">
+        <v>567.96</v>
+      </c>
+      <c r="B181" s="5" t="n">
+        <v>-689.22</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="4" t="n">
+        <v>543.34</v>
+      </c>
+      <c r="B182" s="5" t="n">
+        <v>-577.54</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="4" t="n">
+        <v>332.29</v>
+      </c>
+      <c r="B183" s="5" t="n">
+        <v>-909.95</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="4" t="n">
+        <v>485.3</v>
+      </c>
+      <c r="B184" s="5" t="n">
+        <v>-587.21</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="4" t="n">
+        <v>413.19</v>
+      </c>
+      <c r="B185" s="5" t="n">
+        <v>-606.56</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="4" t="n">
+        <v>450</v>
+      </c>
+      <c r="B186" s="5" t="n">
+        <v>-550</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="4" t="n">
+        <v>69.35</v>
+      </c>
+      <c r="B187" s="5" t="n">
+        <v>-947.76</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="4" t="n">
+        <v>422.86</v>
+      </c>
+      <c r="B188" s="5" t="n">
+        <v>-491.36</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="4" t="n">
+        <v>133.39</v>
+      </c>
+      <c r="B189" s="5" t="n">
+        <v>-262.22</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="4" t="n">
+        <v>439.63</v>
+      </c>
+      <c r="B190" s="5" t="n">
+        <v>-459.42</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="4" t="n">
+        <v>482.16</v>
+      </c>
+      <c r="B191" s="5" t="n">
+        <v>-433.9</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="4" t="n">
+        <v>384.72</v>
+      </c>
+      <c r="B192" s="5" t="n">
+        <v>-159.36</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="4" t="n">
+        <v>443.49</v>
+      </c>
+      <c r="B193" s="5" t="n">
+        <v>-295.47</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="4" t="n">
+        <v>366.16</v>
+      </c>
+      <c r="B194" s="5" t="n">
+        <v>53.3</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="4" t="n">
+        <v>450</v>
+      </c>
+      <c r="B195" s="5" t="n">
+        <v>-250</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="4" t="n">
+        <v>471.33</v>
+      </c>
+      <c r="B196" s="5" t="n">
+        <v>-153.95</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="0" t="n">
+        <v>499.95</v>
+      </c>
+      <c r="B197" s="6" t="n">
+        <v>-314.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Página &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D196"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="17.27"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="str">
+        <f aca="false">D4</f>
+        <v>#AA5555</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
+        <v>592.63</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>-46.22</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
+        <v>972.57</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>282.84</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
+        <v>797.21</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>27.38</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
+        <v>800.46</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>-13.75</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="n">
+        <v>885.97</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>55.53</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="n">
+        <v>775.56</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>-71.12</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="n">
+        <v>809.12</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>-185.86</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
+        <v>716.03</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>-190.93</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="n">
+        <v>1069.98</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>98.82</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="n">
+        <v>848.09</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>-196.68</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="n">
+        <v>984.47</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>-77.61</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="n">
+        <v>862.16</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>-221.58</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="n">
+        <v>969.32</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>-180.44</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="n">
+        <v>891.38</v>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>-245.39</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="n">
+        <v>1087.3</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>-133.9</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="n">
+        <v>1006.12</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>-245.39</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="n">
+        <v>1102.46</v>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>-228.07</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="n">
+        <v>1232.94</v>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>-225.05</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="n">
+        <v>988.97</v>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>-415.35</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="n">
+        <v>1080.05</v>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>-499.93</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="n">
+        <v>999.54</v>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>-540.59</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="n">
+        <v>1050.77</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>-591.02</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="n">
+        <v>951.56</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>-575.56</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="n">
+        <v>1111.77</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>-672.34</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="n">
+        <v>949.93</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>-617.85</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="n">
+        <v>1063.19</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>-721.35</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="n">
+        <v>835.12</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>-635.65</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="n">
+        <v>1086.57</v>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>-788.64</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="n">
+        <v>1014.32</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>-821.93</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="n">
+        <v>822.22</v>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>-782.19</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="n">
+        <v>1139.16</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>-1031.58</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="n">
+        <v>760.61</v>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>-777.74</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="n">
+        <v>845.97</v>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>-889.82</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="n">
+        <v>777.69</v>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>-860.13</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="n">
+        <v>824.45</v>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>-931.38</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="n">
+        <v>689.36</v>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>-887.59</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="n">
+        <v>790.3</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>-988.53</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="n">
+        <v>724.24</v>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>-973.69</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="n">
+        <v>643.34</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>-863.1</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="n">
+        <v>581.73</v>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>-838.6</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="n">
+        <v>426.61</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>-1076.86</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4" t="n">
+        <v>412.5</v>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>-922.48</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4" t="n">
+        <v>489.29</v>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>-760.61</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4" t="n">
+        <v>515.15</v>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>-788.93</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="n">
+        <v>182.06</v>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>-1089.39</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="n">
+        <v>350.76</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>-738.45</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="n">
+        <v>243.01</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>-942.24</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="n">
+        <v>102.02</v>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>-880.67</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>-781.55</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>-804.33</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="n">
+        <v>155.59</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>-723.67</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="n">
+        <v>256.58</v>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>-628.47</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4" t="n">
+        <v>-12.11</v>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>-751.36</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="n">
+        <v>240.61</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>-525.71</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="n">
+        <v>300.32</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>-509.05</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4" t="n">
+        <v>158.68</v>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>-527.8</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="4" t="n">
+        <v>335.73</v>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>-438.93</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4" t="n">
+        <v>173.96</v>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>-481.28</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4" t="n">
+        <v>270.46</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>-422.27</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="4" t="n">
+        <v>243.39</v>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>-463.92</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="4" t="n">
+        <v>-22.53</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>-270.22</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="4" t="n">
+        <v>288.51</v>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>-374.36</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="4" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>-171.63</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="4" t="n">
+        <v>289.21</v>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>-291.74</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="4" t="n">
+        <v>263.18</v>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>-107.94</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="4" t="n">
+        <v>239.98</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>-6.97</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="n">
+        <v>303.43</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>-133.18</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="n">
+        <v>141.2</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>227.49</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="4" t="n">
+        <v>410.18</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>-159.46</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="4" t="n">
+        <v>381.86</v>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>252.97</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4" t="n">
+        <v>500.78</v>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>41.57</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4" t="n">
+        <v>476.24</v>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>296.38</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="4" t="n">
+        <v>547.97</v>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>-8.45</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="4" t="n">
+        <v>606.48</v>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>116.12</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B84" s="1" t="str">
+        <f aca="false">D3</f>
+        <v>#FFBB66</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B85" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="4" t="n">
+        <v>287.52</v>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>-348.51</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="4" t="n">
+        <v>257.66</v>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>-159.62</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="4" t="n">
+        <v>372.64</v>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>-232.79</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="4" t="n">
+        <v>274.09</v>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="4" t="n">
+        <v>426.39</v>
+      </c>
+      <c r="B91" s="5" t="n">
+        <v>-268.62</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="4" t="n">
+        <v>468.95</v>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>-238.76</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="4" t="n">
+        <v>436.85</v>
+      </c>
+      <c r="B93" s="5" t="n">
+        <v>-326.11</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>-250</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="4" t="n">
+        <v>515.98</v>
+      </c>
+      <c r="B95" s="5" t="n">
+        <v>-300.73</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="4" t="n">
+        <v>600</v>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="4" t="n">
+        <v>582.43</v>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>-299.24</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="4" t="n">
+        <v>700</v>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>-250</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="4" t="n">
+        <v>668.29</v>
+      </c>
+      <c r="B99" s="5" t="n">
+        <v>-308.19</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="4" t="n">
+        <v>784.76</v>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>-258.92</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="4" t="n">
+        <v>735.49</v>
+      </c>
+      <c r="B101" s="5" t="n">
+        <v>-347.76</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="4" t="n">
+        <v>835.53</v>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>-323.13</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="4" t="n">
+        <v>855.47</v>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>-383.34</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="4" t="n">
+        <v>845.89</v>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>-459.95</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="4" t="n">
+        <v>862.76</v>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>-588.99</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="4" t="n">
+        <v>763.36</v>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>-578.04</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="4" t="n">
+        <v>753.38</v>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>-624.97</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="4" t="n">
+        <v>720.57</v>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>-631.44</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="4" t="n">
+        <v>725.19</v>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>-681.35</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="4" t="n">
+        <v>685.45</v>
+      </c>
+      <c r="B110" s="5" t="n">
+        <v>-768.22</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="4" t="n">
+        <v>654.03</v>
+      </c>
+      <c r="B111" s="5" t="n">
+        <v>-700.76</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="4" t="n">
+        <v>643.86</v>
+      </c>
+      <c r="B112" s="5" t="n">
+        <v>-768.22</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="4" t="n">
+        <v>625.84</v>
+      </c>
+      <c r="B113" s="5" t="n">
+        <v>-693.82</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="4" t="n">
+        <v>567.62</v>
+      </c>
+      <c r="B114" s="5" t="n">
+        <v>-778.85</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="4" t="n">
+        <v>520.03</v>
+      </c>
+      <c r="B115" s="5" t="n">
+        <v>-709.07</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="4" t="n">
+        <v>538.05</v>
+      </c>
+      <c r="B116" s="5" t="n">
+        <v>-589.85</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="4" t="n">
+        <v>481.67</v>
+      </c>
+      <c r="B117" s="5" t="n">
+        <v>-745.58</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="4" t="n">
+        <v>456.26</v>
+      </c>
+      <c r="B118" s="5" t="n">
+        <v>-601.41</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="4" t="n">
+        <v>412.46</v>
+      </c>
+      <c r="B119" s="5" t="n">
+        <v>-772.14</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="4" t="n">
+        <v>350</v>
+      </c>
+      <c r="B120" s="5" t="n">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="4" t="n">
+        <v>407.8</v>
+      </c>
+      <c r="B121" s="5" t="n">
+        <v>-704.85</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="4" t="n">
+        <v>211.92</v>
+      </c>
+      <c r="B122" s="5" t="n">
+        <v>-670.87</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="4" t="n">
+        <v>377.82</v>
+      </c>
+      <c r="B123" s="5" t="n">
+        <v>-620.9</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="4" t="n">
+        <v>244.57</v>
+      </c>
+      <c r="B124" s="5" t="n">
+        <v>-642.89</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="4" t="n">
+        <v>329.3</v>
+      </c>
+      <c r="B125" s="5" t="n">
+        <v>-566.07</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="4" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="B126" s="5" t="n">
+        <v>-739.96</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="B127" s="5" t="n">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="4" t="n">
+        <v>211.57</v>
+      </c>
+      <c r="B128" s="5" t="n">
+        <v>-499.76</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="4" t="n">
+        <v>330.2</v>
+      </c>
+      <c r="B129" s="5" t="n">
+        <v>-438.6</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="4" t="n">
+        <v>271.99</v>
+      </c>
+      <c r="B130" s="5" t="n">
+        <v>-417.23</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="4" t="n">
+        <v>115.71</v>
+      </c>
+      <c r="B131" s="5" t="n">
+        <v>-309.17</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B134" s="1" t="str">
+        <f aca="false">D2</f>
+        <v>#FFFF88</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B135" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="4" t="n">
+        <v>355.05</v>
+      </c>
+      <c r="B137" s="5" t="n">
+        <v>-385.28</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="4" t="n">
+        <v>385.02</v>
+      </c>
+      <c r="B138" s="5" t="n">
+        <v>-351.24</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="4" t="n">
+        <v>408.85</v>
+      </c>
+      <c r="B139" s="5" t="n">
+        <v>-360.77</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="4" t="n">
+        <v>462.64</v>
+      </c>
+      <c r="B140" s="5" t="n">
+        <v>-342.38</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="4" t="n">
+        <v>578.41</v>
+      </c>
+      <c r="B141" s="5" t="n">
+        <v>-256.58</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="4" t="n">
+        <v>587.26</v>
+      </c>
+      <c r="B142" s="5" t="n">
+        <v>-352.6</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="4" t="n">
+        <v>647.18</v>
+      </c>
+      <c r="B143" s="5" t="n">
+        <v>-319.91</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="4" t="n">
+        <v>713.24</v>
+      </c>
+      <c r="B144" s="5" t="n">
+        <v>-348.51</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="4" t="n">
+        <v>706.43</v>
+      </c>
+      <c r="B145" s="5" t="n">
+        <v>-400.95</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="4" t="n">
+        <v>778.61</v>
+      </c>
+      <c r="B146" s="5" t="n">
+        <v>-421.38</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="4" t="n">
+        <v>749.33</v>
+      </c>
+      <c r="B147" s="5" t="n">
+        <v>-563.01</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="4" t="n">
+        <v>686</v>
+      </c>
+      <c r="B148" s="5" t="n">
+        <v>-648.82</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="4" t="n">
+        <v>612.46</v>
+      </c>
+      <c r="B149" s="5" t="n">
+        <v>-686.27</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="4" t="n">
+        <v>507.59</v>
+      </c>
+      <c r="B150" s="5" t="n">
+        <v>-599.11</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="4" t="n">
+        <v>450</v>
+      </c>
+      <c r="B151" s="5" t="n">
+        <v>-650</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="4" t="n">
+        <v>381.61</v>
+      </c>
+      <c r="B152" s="5" t="n">
+        <v>-603.87</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="4" t="n">
+        <v>303.98</v>
+      </c>
+      <c r="B153" s="5" t="n">
+        <v>-542.59</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="4" t="n">
+        <v>330.54</v>
+      </c>
+      <c r="B154" s="5" t="n">
+        <v>-448.61</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="4" t="n">
+        <v>400.68</v>
+      </c>
+      <c r="B155" s="5" t="n">
+        <v>-443.17</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B158" s="1" t="str">
+        <f aca="false">D1</f>
+        <v>#FFFFDD</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B159" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="4" t="n">
+        <v>442.33</v>
+      </c>
+      <c r="B161" s="5" t="n">
+        <v>-426.23</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="4" t="n">
+        <v>508.26</v>
+      </c>
+      <c r="B162" s="5" t="n">
+        <v>-377.46</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="4" t="n">
+        <v>601.52</v>
+      </c>
+      <c r="B163" s="5" t="n">
+        <v>-430.52</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="4" t="n">
+        <v>630.99</v>
+      </c>
+      <c r="B164" s="5" t="n">
+        <v>-399.97</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="4" t="n">
+        <v>667.44</v>
+      </c>
+      <c r="B165" s="5" t="n">
+        <v>-428.37</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="4" t="n">
+        <v>740.87</v>
+      </c>
+      <c r="B166" s="5" t="n">
+        <v>-511.99</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="4" t="n">
+        <v>671.73</v>
+      </c>
+      <c r="B167" s="5" t="n">
+        <v>-566.66</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="4" t="n">
+        <v>660.47</v>
+      </c>
+      <c r="B168" s="5" t="n">
+        <v>-593.99</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="4" t="n">
+        <v>579.54</v>
+      </c>
+      <c r="B169" s="5" t="n">
+        <v>-584.88</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="4" t="n">
+        <v>468.59</v>
+      </c>
+      <c r="B170" s="5" t="n">
+        <v>-565.58</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="4" t="n">
+        <v>426.79</v>
+      </c>
+      <c r="B171" s="5" t="n">
+        <v>-607.93</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="4" t="n">
+        <v>440.19</v>
+      </c>
+      <c r="B172" s="5" t="n">
+        <v>-548.97</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="4" t="n">
+        <v>364.61</v>
+      </c>
+      <c r="B173" s="5" t="n">
+        <v>-576.84</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="4" t="n">
+        <v>406.96</v>
+      </c>
+      <c r="B174" s="5" t="n">
+        <v>-517.35</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="4" t="n">
+        <v>321.74</v>
+      </c>
+      <c r="B175" s="5" t="n">
+        <v>-524.31</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="4" t="n">
+        <v>376.41</v>
+      </c>
+      <c r="B176" s="5" t="n">
+        <v>-472.86</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="4" t="n">
+        <v>351.75</v>
+      </c>
+      <c r="B177" s="5" t="n">
+        <v>-406.94</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="4" t="n">
+        <v>426.79</v>
+      </c>
+      <c r="B178" s="5" t="n">
+        <v>-453.03</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B181" s="1" t="str">
+        <f aca="false">D5</f>
+        <v>#777799</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B182" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="4" t="n">
+        <v>467.32</v>
+      </c>
+      <c r="B184" s="5" t="n">
+        <v>-517.91</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="4" t="n">
+        <v>503.49</v>
+      </c>
+      <c r="B185" s="5" t="n">
+        <v>-536.46</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="4" t="n">
+        <v>561.91</v>
+      </c>
+      <c r="B186" s="5" t="n">
+        <v>-545.27</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="4" t="n">
+        <v>620</v>
+      </c>
+      <c r="B187" s="5" t="n">
+        <v>-520</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="4" t="n">
+        <v>650</v>
+      </c>
+      <c r="B188" s="5" t="n">
+        <v>-473.4</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="4" t="n">
+        <v>620.33</v>
+      </c>
+      <c r="B189" s="5" t="n">
+        <v>-430.75</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="4" t="n">
+        <v>600.86</v>
+      </c>
+      <c r="B190" s="5" t="n">
+        <v>-396.44</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="4" t="n">
+        <v>548.93</v>
+      </c>
+      <c r="B191" s="5" t="n">
+        <v>-401.07</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="4" t="n">
+        <v>484.48</v>
+      </c>
+      <c r="B192" s="5" t="n">
+        <v>-401.54</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="4" t="n">
+        <v>449.24</v>
+      </c>
+      <c r="B193" s="5" t="n">
+        <v>-439.56</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="4" t="n">
+        <v>424.2</v>
+      </c>
+      <c r="B194" s="5" t="n">
+        <v>-470.62</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="4" t="n">
+        <v>431.62</v>
+      </c>
+      <c r="B195" s="5" t="n">
+        <v>-504</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="4" t="n">
+        <v>493.29</v>
+      </c>
+      <c r="B196" s="7"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Página &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D140"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="17.39"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="str">
+        <f aca="false">D4</f>
+        <v>#AA5555</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
+        <v>217.11</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>-134.58</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
+        <v>214.68</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>-22.02</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
+        <v>208.2</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>67.06</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
+        <v>246.26</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>15.23</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="n">
+        <v>280.28</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>61.39</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="n">
+        <v>313.48</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>37.1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="n">
+        <v>370.97</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>63.82</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="n">
+        <v>333.72</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>-7.44</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
+        <v>390.41</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>-19.59</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="n">
+        <v>486.77</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>54.1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="n">
+        <v>623.63</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>72.73</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="n">
+        <v>617.96</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>35.48</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="n">
+        <v>771.01</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>71.92</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="n">
+        <v>811.5</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="n">
+        <v>919.32</v>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>-16.77</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="n">
+        <v>1093.4</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>49.7</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="n">
+        <v>1122.52</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="n">
+        <v>1084.54</v>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>-90.83</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="n">
+        <v>960.47</v>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>-211.75</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="n">
+        <v>968.7</v>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>-247.2</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="n">
+        <v>1095.3</v>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>-174.4</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="n">
+        <v>1075.68</v>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>-297.84</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="n">
+        <v>1115.17</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>-339.19</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="n">
+        <v>992.7</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>-443.17</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="n">
+        <v>1016.3</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>-536.3</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="n">
+        <v>1092.21</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>-580.32</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="n">
+        <v>1205.76</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>-616.68</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="n">
+        <v>1186.62</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>-647.93</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="n">
+        <v>1070.52</v>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>-668.35</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="n">
+        <v>976.11</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>-643.47</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="n">
+        <v>1042.61</v>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>-734.56</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="n">
+        <v>1117.42</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>-810.85</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="n">
+        <v>1075.94</v>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>-871.59</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="n">
+        <v>969.27</v>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>-906.41</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="n">
+        <v>1038.9</v>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>-945.67</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="n">
+        <v>969.27</v>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>-951.6</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="n">
+        <v>906.46</v>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>-986.33</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="n">
+        <v>743.13</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>-1031.73</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="n">
+        <v>628.88</v>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>-1028.07</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="n">
+        <v>382.67</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>-1020.61</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="n">
+        <v>223.57</v>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>-982.26</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="n">
+        <v>191.74</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>-917.81</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>-850</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4" t="n">
+        <v>124.02</v>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>-758.7</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4" t="n">
+        <v>220.3</v>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>-574.29</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="n">
+        <v>134.25</v>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>-560.26</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="n">
+        <v>92.03</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>-527.35</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="n">
+        <v>36.77</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>-477.06</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>-418.69</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="n">
+        <v>133.01</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>-335.49</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="n">
+        <v>131.14</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>-266.57</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="n">
+        <v>212.48</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>-217.52</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="n">
+        <v>177.6</v>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>-174.32</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B61" s="1" t="str">
+        <f aca="false">D3</f>
+        <v>#FFBB66</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4" t="n">
+        <v>306.19</v>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>-361.71</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4" t="n">
+        <v>320.29</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>-298.69</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="4" t="n">
+        <v>363.41</v>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>-256.4</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="4" t="n">
+        <v>402.39</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>-190.05</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="4" t="n">
+        <v>491.95</v>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>-186.74</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="4" t="n">
+        <v>588.98</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>-224.88</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="4" t="n">
+        <v>705.9</v>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>-85.57</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="4" t="n">
+        <v>922.34</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>97.7</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="4" t="n">
+        <v>900</v>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="4" t="n">
+        <v>817.03</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>-170.98</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="n">
+        <v>760.64</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>-282.93</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="n">
+        <v>731.61</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>-382.45</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="4" t="n">
+        <v>896.64</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>-416.45</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="4" t="n">
+        <v>1171.96</v>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>-248.1</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4" t="n">
+        <v>950.54</v>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>-483.62</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4" t="n">
+        <v>1014.39</v>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>-563.23</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="4" t="n">
+        <v>1211.76</v>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>-634.54</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="4" t="n">
+        <v>1129.66</v>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>-655.28</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="4" t="n">
+        <v>854.34</v>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>-607.18</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="4" t="n">
+        <v>850</v>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>-750</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="4" t="n">
+        <v>722.55</v>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>-833.88</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="4" t="n">
+        <v>581.62</v>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>-845.05</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>-850</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="4" t="n">
+        <v>409.49</v>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>-795.87</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="4" t="n">
+        <v>390.95</v>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>-723.01</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="4" t="n">
+        <v>294.99</v>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>-633.45</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="4" t="n">
+        <v>345.53</v>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>-512.55</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="B91" s="5" t="n">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="4" t="n">
+        <v>326.98</v>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>-426.19</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B95" s="1" t="str">
+        <f aca="false">D2</f>
+        <v>#FFFF88</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B96" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="4" t="n">
+        <v>388.21</v>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>-512.82</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="4" t="n">
+        <v>364.11</v>
+      </c>
+      <c r="B99" s="5" t="n">
+        <v>-442.71</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="4" t="n">
+        <v>403.54</v>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>-374.79</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="4" t="n">
+        <v>455.39</v>
+      </c>
+      <c r="B101" s="5" t="n">
+        <v>-314.18</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="4" t="n">
+        <v>548.14</v>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>-267.44</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="4" t="n">
+        <v>610.83</v>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>-217.67</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="4" t="n">
+        <v>788.21</v>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>-209.18</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="4" t="n">
+        <v>897.66</v>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>-281.83</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="4" t="n">
+        <v>949.55</v>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>-370.52</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="4" t="n">
+        <v>893.88</v>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>-492.23</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="4" t="n">
+        <v>894.83</v>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>-612.06</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="4" t="n">
+        <v>903.32</v>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>-686.6</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="4" t="n">
+        <v>778.78</v>
+      </c>
+      <c r="B110" s="5" t="n">
+        <v>-728.11</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="4" t="n">
+        <v>654.23</v>
+      </c>
+      <c r="B111" s="5" t="n">
+        <v>-807.37</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="4" t="n">
+        <v>559.88</v>
+      </c>
+      <c r="B112" s="5" t="n">
+        <v>-804.54</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="4" t="n">
+        <v>448.55</v>
+      </c>
+      <c r="B113" s="5" t="n">
+        <v>-783.78</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="4" t="n">
+        <v>391.93</v>
+      </c>
+      <c r="B114" s="5" t="n">
+        <v>-746.04</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="4" t="n">
+        <v>419.3</v>
+      </c>
+      <c r="B115" s="5" t="n">
+        <v>-667.73</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="4" t="n">
+        <v>364.57</v>
+      </c>
+      <c r="B116" s="5" t="n">
+        <v>-605.46</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="4" t="n">
+        <v>464.59</v>
+      </c>
+      <c r="B117" s="5" t="n">
+        <v>-578.09</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="4" t="n">
+        <v>385.33</v>
+      </c>
+      <c r="B118" s="5" t="n">
+        <v>-555.45</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B121" s="1" t="str">
+        <f aca="false">D5</f>
+        <v>#777799</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B122" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="4" t="n">
+        <v>509.55</v>
+      </c>
+      <c r="B124" s="5" t="n">
+        <v>-693.09</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="4" t="n">
+        <v>639.8</v>
+      </c>
+      <c r="B125" s="5" t="n">
+        <v>-683.74</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="4" t="n">
+        <v>729.03</v>
+      </c>
+      <c r="B126" s="5" t="n">
+        <v>-626.89</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="4" t="n">
+        <v>771.48</v>
+      </c>
+      <c r="B127" s="5" t="n">
+        <v>-506</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="4" t="n">
+        <v>808.9</v>
+      </c>
+      <c r="B128" s="5" t="n">
+        <v>-393.03</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="4" t="n">
+        <v>739.82</v>
+      </c>
+      <c r="B129" s="5" t="n">
+        <v>-344.1</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="4" t="n">
+        <v>685.13</v>
+      </c>
+      <c r="B130" s="5" t="n">
+        <v>-400.94</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="4" t="n">
+        <v>664.26</v>
+      </c>
+      <c r="B131" s="5" t="n">
+        <v>-336.9</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="4" t="n">
+        <v>593.03</v>
+      </c>
+      <c r="B132" s="5" t="n">
+        <v>-362.09</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="4" t="n">
+        <v>535.46</v>
+      </c>
+      <c r="B133" s="5" t="n">
+        <v>-372.16</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="4" t="n">
+        <v>469.26</v>
+      </c>
+      <c r="B134" s="5" t="n">
+        <v>-400.94</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="4" t="n">
+        <v>519.63</v>
+      </c>
+      <c r="B135" s="5" t="n">
+        <v>-449.88</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="4" t="n">
+        <v>428.24</v>
+      </c>
+      <c r="B136" s="5" t="n">
+        <v>-483.7</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="4" t="n">
+        <v>385.79</v>
+      </c>
+      <c r="B137" s="5" t="n">
+        <v>-550.62</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="4" t="n">
+        <v>442.63</v>
+      </c>
+      <c r="B138" s="5" t="n">
+        <v>-590.91</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="4" t="n">
+        <v>409.53</v>
+      </c>
+      <c r="B139" s="5" t="n">
+        <v>-652.08</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="4" t="n">
+        <v>456.3</v>
+      </c>
+      <c r="B140" s="5" t="n">
+        <v>-679.42</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Página &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="17.85"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="str">
+        <f aca="false">D5</f>
+        <v>#777799</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
+        <v>904.87</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>-55.46</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
+        <v>103.137</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>-52.83</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
+        <v>99.974</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>-146.39</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="n">
+        <v>102.214</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>-216.23</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="n">
+        <v>104.982</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>-243.9</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="n">
+        <v>104.982</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>-304.51</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="n">
+        <v>102.346</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>-382.26</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
+        <v>100.106</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>-445.51</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="n">
+        <v>970.75</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>-502.17</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="n">
+        <v>104.323</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>-552.24</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="n">
+        <v>952.31</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>-540.39</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="n">
+        <v>979.98</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>-578.6</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="n">
+        <v>101.292</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>-662.93</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="n">
+        <v>104.323</v>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>-742</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="n">
+        <v>1100</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>-800</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="n">
+        <v>939.13</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>-888.26</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="n">
+        <v>808.67</v>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>-868.5</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="n">
+        <v>733.56</v>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>-880.36</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="n">
+        <v>600</v>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="n">
+        <v>502.96</v>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>-867.18</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="n">
+        <v>385.68</v>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>-927.8</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="n">
+        <v>255.23</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>-898.81</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Página &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D45"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="17.27"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="str">
+        <f aca="false">D5</f>
+        <v>#777799</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
+        <v>35.14</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>33.82</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
+        <v>76.02</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
+        <v>44.68</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>138.74</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
+        <v>129.17</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>151.01</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="n">
+        <v>238.19</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>121.03</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="n">
+        <v>274.98</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>246.4</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="n">
+        <v>442.59</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>319.98</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="n">
+        <v>501.19</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>242.31</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
+        <v>659.26</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>300.91</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="n">
+        <v>757.38</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>277.74</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="n">
+        <v>751.93</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>219.14</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="n">
+        <v>779.18</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>182.35</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="n">
+        <v>880.02</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>245.04</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="n">
+        <v>960.42</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>272.29</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="n">
+        <v>1010.84</v>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>238.22</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="n">
+        <v>1062.63</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>186.44</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="n">
+        <v>1073.53</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>41.99</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="n">
+        <v>1126.67</v>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>-79.29</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="n">
+        <v>1212.53</v>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>-192.39</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="n">
+        <v>1121.22</v>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>-325.94</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="n">
+        <v>1181.18</v>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>-410.43</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="n">
+        <v>1185.27</v>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>-497.64</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="n">
+        <v>1148.48</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>-627.1</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="n">
+        <v>1013.57</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>-669.34</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="n">
+        <v>1148.48</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>-777</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="n">
+        <v>1130.76</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>-868.3</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="n">
+        <v>1053.09</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>-944.61</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="n">
+        <v>901.83</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>-1016.83</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="n">
+        <v>700</v>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="n">
+        <v>442.59</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>-1064.53</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="n">
+        <v>131.9</v>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>-933.71</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="n">
+        <v>22.88</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>-871.02</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="n">
+        <v>21.52</v>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>-790.62</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>-719.76</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="n">
+        <v>-62.97</v>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>-667.98</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="n">
+        <v>-132.47</v>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>-546.7</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="n">
+        <v>-64.33</v>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>-417.24</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="n">
+        <v>-112.03</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>-248.27</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="n">
+        <v>-77.96</v>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>-65.66</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="n">
+        <v>-27.54</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>21.55</v>
       </c>
     </row>
   </sheetData>

--- a/fotogramas.xlsx
+++ b/fotogramas.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="14"/>
   </bookViews>
   <sheets>
     <sheet name="F0" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,6 +22,7 @@
     <sheet name="F11" sheetId="12" state="visible" r:id="rId14"/>
     <sheet name="F12" sheetId="13" state="visible" r:id="rId15"/>
     <sheet name="F13" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="Hoja15" sheetId="15" state="visible" r:id="rId17"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="25">
   <si>
     <t xml:space="preserve">CAPA</t>
   </si>
@@ -91,6 +92,24 @@
   <si>
     <t xml:space="preserve">EXPLOCION 1</t>
   </si>
+  <si>
+    <t xml:space="preserve">EXPLOCION 02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FONDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#DDDDDD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPLOCION 03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPLOCION 04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPLOCION 05</t>
+  </si>
 </sst>
 </file>
 
@@ -99,7 +118,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -135,8 +154,22 @@
       <family val="3"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color theme="2"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -147,6 +180,18 @@
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.6"/>
         <bgColor rgb="FF33CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.25"/>
+        <bgColor rgb="FF0066CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
+        <bgColor rgb="FFCCFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -184,7 +229,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -213,8 +258,32 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -262,7 +331,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFC4FEBB"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF78CCFD"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -276,7 +345,7 @@
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF024F7A"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
@@ -1019,7 +1088,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D167"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16.92"/>
@@ -1097,298 +1166,1324 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
+      <c r="A6" s="5" t="n">
+        <v>132.05</v>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>-910.96</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
+      <c r="A7" s="5" t="n">
+        <v>-44</v>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>-890.69</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6"/>
+      <c r="A8" s="5" t="n">
+        <v>-113.35</v>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>-821.33</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6"/>
+      <c r="A9" s="5" t="n">
+        <v>-205.11</v>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>-873.61</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5"/>
-      <c r="B10" s="6"/>
+      <c r="A10" s="5" t="n">
+        <v>-293.67</v>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>-828.8</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5"/>
-      <c r="B11" s="6"/>
+      <c r="A11" s="5" t="n">
+        <v>-274.46</v>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>-492.71</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6"/>
+      <c r="A12" s="5" t="n">
+        <v>-189.1</v>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>-535.39</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5"/>
-      <c r="B13" s="6"/>
+      <c r="A13" s="5" t="n">
+        <v>-160.3</v>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>-498.05</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5"/>
-      <c r="B14" s="6"/>
+      <c r="A14" s="5" t="n">
+        <v>-248.85</v>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>-356.14</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6"/>
+      <c r="A15" s="5" t="n">
+        <v>-160.3</v>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>-233.44</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5"/>
-      <c r="B16" s="6"/>
+      <c r="A16" s="5" t="n">
+        <v>-110.15</v>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>-257.98</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5"/>
-      <c r="B17" s="6"/>
+      <c r="A17" s="5" t="n">
+        <v>-67.47</v>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>-182.23</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5"/>
-      <c r="B18" s="6"/>
+      <c r="A18" s="5" t="n">
+        <v>-82.41</v>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>-117.14</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5"/>
-      <c r="B19" s="6"/>
+      <c r="A19" s="5" t="n">
+        <v>44.56</v>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>-55.26</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5"/>
-      <c r="B20" s="6"/>
+      <c r="A20" s="5" t="n">
+        <v>133.12</v>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>-164.09</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5"/>
-      <c r="B21" s="6"/>
+      <c r="A21" s="5" t="n">
+        <v>193.93</v>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>-149.15</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5"/>
-      <c r="B22" s="6"/>
+      <c r="A22" s="5" t="n">
+        <v>193.93</v>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>-86.2</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5"/>
-      <c r="B23" s="6"/>
+      <c r="A23" s="5" t="n">
+        <v>159.79</v>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>-74.46</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5"/>
-      <c r="B24" s="6"/>
+      <c r="A24" s="5" t="n">
+        <v>184.33</v>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>-31.79</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5"/>
-      <c r="B25" s="6"/>
+      <c r="A25" s="5" t="n">
+        <v>264.35</v>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>-73.4</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5"/>
-      <c r="B26" s="6"/>
+      <c r="A26" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5"/>
-      <c r="B27" s="6"/>
+      <c r="A27" s="5" t="n">
+        <v>351.84</v>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>-46.72</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5"/>
-      <c r="B28" s="6"/>
+      <c r="A28" s="5" t="n">
+        <v>441.47</v>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>-52.06</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5"/>
-      <c r="B29" s="6"/>
+      <c r="A29" s="5" t="n">
+        <v>530.02</v>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>-20.05</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5"/>
-      <c r="B30" s="6"/>
+      <c r="A30" s="5" t="n">
+        <v>535.36</v>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>-70.2</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5"/>
-      <c r="B31" s="6"/>
+      <c r="A31" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5"/>
-      <c r="B32" s="6"/>
+      <c r="A32" s="5" t="n">
+        <v>676.2</v>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>-81.93</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5"/>
-      <c r="B33" s="6"/>
+      <c r="A33" s="5" t="n">
+        <v>698.6</v>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>-133.15</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5"/>
-      <c r="B34" s="6"/>
+      <c r="A34" s="5" t="n">
+        <v>642.05</v>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>-185.43</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5"/>
-      <c r="B35" s="6"/>
+      <c r="A35" s="5" t="n">
+        <v>676.2</v>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>-260.12</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5"/>
-      <c r="B36" s="6"/>
+      <c r="A36" s="5" t="n">
+        <v>780.76</v>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>-276.12</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5"/>
-      <c r="B37" s="6"/>
+      <c r="A37" s="5" t="n">
+        <v>887.45</v>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>-188.63</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="5"/>
-      <c r="B38" s="6"/>
+      <c r="A38" s="5" t="n">
+        <v>978.14</v>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>-183.29</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5"/>
-      <c r="B39" s="6"/>
+      <c r="A39" s="5" t="n">
+        <v>1047.5</v>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>-252.65</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5"/>
-      <c r="B40" s="6"/>
+      <c r="A40" s="5" t="n">
+        <v>976.01</v>
+      </c>
+      <c r="B40" s="6" t="n">
+        <v>-335.87</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="5"/>
-      <c r="B41" s="6"/>
+      <c r="A41" s="5" t="n">
+        <v>953.6</v>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>-434.03</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="5"/>
-      <c r="B42" s="6"/>
+      <c r="A42" s="5" t="n">
+        <v>973.88</v>
+      </c>
+      <c r="B42" s="6" t="n">
+        <v>-526.85</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="5"/>
-      <c r="B43" s="6"/>
+      <c r="A43" s="5" t="n">
+        <v>1033.63</v>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>-577</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="5"/>
-      <c r="B44" s="6"/>
+      <c r="A44" s="5" t="n">
+        <v>1026.16</v>
+      </c>
+      <c r="B44" s="6" t="n">
+        <v>-832</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="5"/>
-      <c r="B45" s="6"/>
+      <c r="A45" s="5" t="n">
+        <v>853.31</v>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>-882.15</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="5"/>
-      <c r="B46" s="6"/>
+      <c r="A46" s="5" t="n">
+        <v>776.49</v>
+      </c>
+      <c r="B46" s="6" t="n">
+        <v>-822.4</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="5"/>
-      <c r="B47" s="6"/>
+      <c r="A47" s="5" t="n">
+        <v>681.53</v>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>-860.81</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="5"/>
-      <c r="B48" s="6"/>
+      <c r="A48" s="5" t="n">
+        <v>644.19</v>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>-903.49</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="5"/>
-      <c r="B49" s="6"/>
+      <c r="A49" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
+      <c r="A50" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2"/>
-      <c r="B51" s="4"/>
+      <c r="A51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" s="2" t="str">
+        <f aca="false">D3</f>
+        <v>#DDAA77</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
+      <c r="A52" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
+      <c r="A53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2"/>
-      <c r="B54" s="2"/>
+      <c r="A54" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B54" s="6" t="n">
+        <v>-900</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="5"/>
-      <c r="B55" s="6"/>
+      <c r="A55" s="5" t="n">
+        <v>58.43</v>
+      </c>
+      <c r="B55" s="6" t="n">
+        <v>-828.8</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="5"/>
-      <c r="B56" s="6"/>
+      <c r="A56" s="5" t="n">
+        <v>138.45</v>
+      </c>
+      <c r="B56" s="6" t="n">
+        <v>-764.78</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="5"/>
-      <c r="B57" s="6"/>
+      <c r="A57" s="5" t="n">
+        <v>124.58</v>
+      </c>
+      <c r="B57" s="6" t="n">
+        <v>-703.97</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="5"/>
-      <c r="B58" s="6"/>
+      <c r="A58" s="5" t="n">
+        <v>221.67</v>
+      </c>
+      <c r="B58" s="6" t="n">
+        <v>-636.75</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="5"/>
-      <c r="B59" s="6"/>
+      <c r="A59" s="5" t="n">
+        <v>263.28</v>
+      </c>
+      <c r="B59" s="6" t="n">
+        <v>-555.66</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="5"/>
-      <c r="B60" s="6"/>
+      <c r="A60" s="5" t="n">
+        <v>419.06</v>
+      </c>
+      <c r="B60" s="6" t="n">
+        <v>-558.86</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="5"/>
-      <c r="B61" s="6"/>
+      <c r="A61" s="5" t="n">
+        <v>460.67</v>
+      </c>
+      <c r="B61" s="6" t="n">
+        <v>-622.88</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="5"/>
-      <c r="B62" s="6"/>
+      <c r="A62" s="5" t="n">
+        <v>554.56</v>
+      </c>
+      <c r="B62" s="6" t="n">
+        <v>-567.4</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="5"/>
-      <c r="B63" s="6"/>
+      <c r="A63" s="5" t="n">
+        <v>643.12</v>
+      </c>
+      <c r="B63" s="6" t="n">
+        <v>-629.28</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="5"/>
-      <c r="B64" s="6"/>
+      <c r="A64" s="5" t="n">
+        <v>623.92</v>
+      </c>
+      <c r="B64" s="6" t="n">
+        <v>-686.9</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="5"/>
-      <c r="B65" s="6"/>
+      <c r="A65" s="5" t="n">
+        <v>669.79</v>
+      </c>
+      <c r="B65" s="6" t="n">
+        <v>-729.57</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="5"/>
-      <c r="B66" s="6"/>
+      <c r="A66" s="5" t="n">
+        <v>631.38</v>
+      </c>
+      <c r="B66" s="6" t="n">
+        <v>-766.92</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="5"/>
-      <c r="B67" s="6"/>
+      <c r="A67" s="5" t="n">
+        <v>644.19</v>
+      </c>
+      <c r="B67" s="6" t="n">
+        <v>-842.67</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="5"/>
-      <c r="B68" s="6"/>
+      <c r="A68" s="5" t="n">
+        <v>548.16</v>
+      </c>
+      <c r="B68" s="6" t="n">
+        <v>-876.81</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="5"/>
-      <c r="B69" s="6"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="6"/>
+      <c r="A69" s="5" t="n">
+        <v>556.7</v>
+      </c>
+      <c r="B69" s="6" t="n">
+        <v>-901.35</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="5"/>
-      <c r="B70" s="6"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="6"/>
+      <c r="A70" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="5"/>
-      <c r="B71" s="6"/>
+      <c r="A71" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="C71" s="5"/>
       <c r="D71" s="6"/>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="5"/>
-      <c r="B72" s="6"/>
+      <c r="A72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B72" s="2" t="str">
+        <f aca="false">D4</f>
+        <v>#FFFF88</v>
+      </c>
       <c r="C72" s="5"/>
       <c r="D72" s="6"/>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="5"/>
-      <c r="B73" s="6"/>
+      <c r="A73" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="C73" s="5"/>
       <c r="D73" s="6"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="C74" s="5"/>
       <c r="D74" s="6"/>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="5" t="n">
+        <v>335.84</v>
+      </c>
+      <c r="B75" s="6" t="n">
+        <v>-910.96</v>
+      </c>
       <c r="C75" s="5"/>
       <c r="D75" s="6"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="5" t="n">
+        <v>314.5</v>
+      </c>
+      <c r="B76" s="6" t="n">
+        <v>-876.81</v>
+      </c>
       <c r="C76" s="5"/>
       <c r="D76" s="6"/>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="5" t="n">
+        <v>353.98</v>
+      </c>
+      <c r="B77" s="6" t="n">
+        <v>-842.67</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="5" t="n">
+        <v>408.39</v>
+      </c>
+      <c r="B78" s="6" t="n">
+        <v>-834.14</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="5" t="n">
+        <v>455.34</v>
+      </c>
+      <c r="B79" s="6" t="n">
+        <v>-874.68</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="5" t="n">
+        <v>439.33</v>
+      </c>
+      <c r="B80" s="6" t="n">
+        <v>-910.96</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B83" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="5" t="n">
+        <v>-78.14</v>
+      </c>
+      <c r="B86" s="6" t="n">
+        <v>-896.02</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="5" t="n">
+        <v>-170.97</v>
+      </c>
+      <c r="B87" s="6" t="n">
+        <v>-890.69</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="5" t="n">
+        <v>-128.29</v>
+      </c>
+      <c r="B88" s="6" t="n">
+        <v>-854.41</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B91" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="5" t="n">
+        <v>-200</v>
+      </c>
+      <c r="B94" s="6" t="n">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="5" t="n">
+        <v>-304.33</v>
+      </c>
+      <c r="B95" s="6" t="n">
+        <v>-450.03</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="5" t="n">
+        <v>-274.46</v>
+      </c>
+      <c r="B96" s="6" t="n">
+        <v>-393.48</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="5" t="n">
+        <v>-196.58</v>
+      </c>
+      <c r="B97" s="6" t="n">
+        <v>-485.54</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B100" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="5" t="n">
+        <v>-86.1</v>
+      </c>
+      <c r="B103" s="6" t="n">
+        <v>-170.01</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="5" t="n">
+        <v>-117.27</v>
+      </c>
+      <c r="B104" s="6" t="n">
+        <v>-205.7</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="5" t="n">
+        <v>-134.86</v>
+      </c>
+      <c r="B105" s="6" t="n">
+        <v>-151.16</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="5" t="n">
+        <v>-96.16</v>
+      </c>
+      <c r="B106" s="6" t="n">
+        <v>-136.07</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B109" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="5" t="n">
+        <v>175.27</v>
+      </c>
+      <c r="B112" s="6" t="n">
+        <v>-117.46</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="5" t="n">
+        <v>127.15</v>
+      </c>
+      <c r="B113" s="6" t="n">
+        <v>-132.6</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="5" t="n">
+        <v>123.62</v>
+      </c>
+      <c r="B114" s="6" t="n">
+        <v>-99.41</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="B115" s="6" t="n">
+        <v>-93.6</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B118" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="5" t="n">
+        <v>435.67</v>
+      </c>
+      <c r="B121" s="6" t="n">
+        <v>-20.63</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="5" t="n">
+        <v>386.04</v>
+      </c>
+      <c r="B122" s="6" t="n">
+        <v>-20.63</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="5" t="n">
+        <v>363.63</v>
+      </c>
+      <c r="B123" s="6" t="n">
+        <v>20.35</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="5" t="n">
+        <v>474.09</v>
+      </c>
+      <c r="B124" s="6" t="n">
+        <v>22.27</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B127" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B128" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="5" t="n">
+        <v>760</v>
+      </c>
+      <c r="B130" s="6" t="n">
+        <v>-240</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="5" t="n">
+        <v>685.8</v>
+      </c>
+      <c r="B131" s="6" t="n">
+        <v>-234.8</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="5" t="n">
+        <v>713.11</v>
+      </c>
+      <c r="B132" s="6" t="n">
+        <v>-194.26</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="5" t="n">
+        <v>783.98</v>
+      </c>
+      <c r="B133" s="6" t="n">
+        <v>-198.95</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B136" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B137" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="5" t="n">
+        <v>916.34</v>
+      </c>
+      <c r="B139" s="6" t="n">
+        <v>-153.5</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="5" t="n">
+        <v>837.44</v>
+      </c>
+      <c r="B140" s="6" t="n">
+        <v>-189.44</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="5" t="n">
+        <v>814.47</v>
+      </c>
+      <c r="B141" s="6" t="n">
+        <v>-163.22</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="5" t="n">
+        <v>915.53</v>
+      </c>
+      <c r="B142" s="6" t="n">
+        <v>-115.13</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B145" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B146" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="5" t="n">
+        <v>1021.12</v>
+      </c>
+      <c r="B148" s="6" t="n">
+        <v>-450.43</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="5" t="n">
+        <v>976.22</v>
+      </c>
+      <c r="B149" s="6" t="n">
+        <v>-449.23</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="5" t="n">
+        <v>985.44</v>
+      </c>
+      <c r="B150" s="6" t="n">
+        <v>-389.3</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="5" t="n">
+        <v>1022.12</v>
+      </c>
+      <c r="B151" s="6" t="n">
+        <v>-364.04</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B154" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B155" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="5" t="n">
+        <v>1062.57</v>
+      </c>
+      <c r="B157" s="6" t="n">
+        <v>-896.46</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="5" t="n">
+        <v>929.36</v>
+      </c>
+      <c r="B158" s="6" t="n">
+        <v>-890.45</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="5" t="n">
+        <v>1055.13</v>
+      </c>
+      <c r="B159" s="6" t="n">
+        <v>-841.86</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B162" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B163" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="5" t="n">
+        <v>815.24</v>
+      </c>
+      <c r="B165" s="6" t="n">
+        <v>-903.52</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="5" t="n">
+        <v>682.96</v>
+      </c>
+      <c r="B166" s="6" t="n">
+        <v>-905.27</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="5" t="n">
+        <v>748.67</v>
+      </c>
+      <c r="B167" s="6" t="n">
+        <v>-868.35</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1406,7 +2501,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D127"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16.92"/>
@@ -1445,8 +2540,8 @@
         <v>8</v>
       </c>
       <c r="B3" s="2" t="str">
-        <f aca="false">D1</f>
-        <v>#555577</v>
+        <f aca="false">D2</f>
+        <v>#884433</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>9</v>
@@ -1484,20 +2579,992 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
+      <c r="A6" s="5" t="n">
+        <v>380.5</v>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>-907.66</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
+      <c r="A7" s="5" t="n">
+        <v>326.06</v>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>-877.17</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6"/>
+      <c r="A8" s="5" t="n">
+        <v>277.44</v>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>-909.47</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6"/>
+      <c r="A9" s="5" t="n">
+        <v>227.72</v>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>-903.66</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="n">
+        <v>176.2</v>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>-856.85</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="n">
+        <v>75.94</v>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>-887.81</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="n">
+        <v>-13.32</v>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>-841.61</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="n">
+        <v>-15.55</v>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>-778.16</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="n">
+        <v>-68.73</v>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>-733.92</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="n">
+        <v>-135.21</v>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>-768.84</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="n">
+        <v>-218.77</v>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>-770.75</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="n">
+        <v>-253.65</v>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>-682.22</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="n">
+        <v>-207.65</v>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>-554.2</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="n">
+        <v>-129.08</v>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>-599.05</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="n">
+        <v>-37.19</v>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>-501.18</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="n">
+        <v>-113.63</v>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>-436.07</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="n">
+        <v>-47.59</v>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>-326.1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="n">
+        <v>-25.62</v>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>-343.03</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="n">
+        <v>-25.26</v>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>-432.71</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="n">
+        <v>46.05</v>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>-446.76</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>-420</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="n">
+        <v>93.23</v>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>-289.73</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="n">
+        <v>35.24</v>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>-288.29</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>-273.52</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>-208.95</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="n">
+        <v>180.4</v>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>-217.45</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="n">
+        <v>255.83</v>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>-161.22</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="n">
+        <v>263.98</v>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>-88.73</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="n">
+        <v>396.43</v>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>-85.29</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="n">
+        <v>402.99</v>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>-130.59</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="n">
+        <v>478.03</v>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>-149.2</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5" t="n">
+        <v>546.73</v>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>-110.3</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5" t="n">
+        <v>627.55</v>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>-190.87</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="n">
+        <v>603.56</v>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>-243.66</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="n">
+        <v>666.42</v>
+      </c>
+      <c r="B40" s="6" t="n">
+        <v>-304.26</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="5" t="n">
+        <v>772.11</v>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>-286.57</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="n">
+        <v>852.68</v>
+      </c>
+      <c r="B42" s="6" t="n">
+        <v>-226.9</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="n">
+        <v>876.84</v>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>-246.88</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5" t="n">
+        <v>855.93</v>
+      </c>
+      <c r="B44" s="6" t="n">
+        <v>-291.02</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="5" t="n">
+        <v>900.08</v>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>-333.78</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="5" t="n">
+        <v>955.84</v>
+      </c>
+      <c r="B46" s="6" t="n">
+        <v>-314.72</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="5" t="n">
+        <v>980</v>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>-340</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="5" t="n">
+        <v>913.01</v>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>-466.63</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="5" t="n">
+        <v>936.58</v>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>-531.82</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="5" t="n">
+        <v>885.97</v>
+      </c>
+      <c r="B50" s="6" t="n">
+        <v>-525.84</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="5" t="n">
+        <v>887.58</v>
+      </c>
+      <c r="B51" s="6" t="n">
+        <v>-552.06</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="5" t="n">
+        <v>937.26</v>
+      </c>
+      <c r="B52" s="6" t="n">
+        <v>-568.95</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="5" t="n">
+        <v>960.88</v>
+      </c>
+      <c r="B53" s="6" t="n">
+        <v>-612.69</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="5" t="n">
+        <v>1027.63</v>
+      </c>
+      <c r="B54" s="6" t="n">
+        <v>-638.61</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="5" t="n">
+        <v>1024.64</v>
+      </c>
+      <c r="B55" s="6" t="n">
+        <v>-651.46</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="5" t="n">
+        <v>950.55</v>
+      </c>
+      <c r="B56" s="6" t="n">
+        <v>-660.63</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="5" t="n">
+        <v>934.51</v>
+      </c>
+      <c r="B57" s="6" t="n">
+        <v>-702.97</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="5" t="n">
+        <v>977.93</v>
+      </c>
+      <c r="B58" s="6" t="n">
+        <v>-742.34</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="5" t="n">
+        <v>971.5</v>
+      </c>
+      <c r="B59" s="6" t="n">
+        <v>-774.51</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="5" t="n">
+        <v>807.77</v>
+      </c>
+      <c r="B60" s="6" t="n">
+        <v>-824.91</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="5" t="n">
+        <v>818.34</v>
+      </c>
+      <c r="B61" s="6" t="n">
+        <v>-753.61</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="5" t="n">
+        <v>771.38</v>
+      </c>
+      <c r="B62" s="6" t="n">
+        <v>-748.2</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="5" t="n">
+        <v>716.28</v>
+      </c>
+      <c r="B63" s="6" t="n">
+        <v>-805.18</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="5" t="n">
+        <v>658.23</v>
+      </c>
+      <c r="B64" s="6" t="n">
+        <v>-745.93</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="5" t="n">
+        <v>636.38</v>
+      </c>
+      <c r="B65" s="6" t="n">
+        <v>-745.7</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="5" t="n">
+        <v>570.02</v>
+      </c>
+      <c r="B66" s="6" t="n">
+        <v>-827.53</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="5" t="n">
+        <v>606.52</v>
+      </c>
+      <c r="B67" s="6" t="n">
+        <v>-887.1</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B70" s="2" t="str">
+        <f aca="false">D3</f>
+        <v>#DDAA77</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="5" t="n">
+        <v>323.55</v>
+      </c>
+      <c r="B73" s="6" t="n">
+        <v>-875.57</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="B74" s="6" t="n">
+        <v>-840</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="5" t="n">
+        <v>193.41</v>
+      </c>
+      <c r="B75" s="6" t="n">
+        <v>-797.16</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="5" t="n">
+        <v>244.26</v>
+      </c>
+      <c r="B76" s="6" t="n">
+        <v>-761.89</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="5" t="n">
+        <v>226.21</v>
+      </c>
+      <c r="B77" s="6" t="n">
+        <v>-727.03</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="5" t="n">
+        <v>308.23</v>
+      </c>
+      <c r="B78" s="6" t="n">
+        <v>-656.5</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="5" t="n">
+        <v>373.85</v>
+      </c>
+      <c r="B79" s="6" t="n">
+        <v>-684.38</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="5" t="n">
+        <v>443.56</v>
+      </c>
+      <c r="B80" s="6" t="n">
+        <v>-622.46</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="5" t="n">
+        <v>457.92</v>
+      </c>
+      <c r="B81" s="6" t="n">
+        <v>-705.3</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="5" t="n">
+        <v>517.38</v>
+      </c>
+      <c r="B82" s="6" t="n">
+        <v>-773.38</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="5" t="n">
+        <v>492.78</v>
+      </c>
+      <c r="B83" s="6" t="n">
+        <v>-836.94</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="5" t="n">
+        <v>535.02</v>
+      </c>
+      <c r="B84" s="6" t="n">
+        <v>-887.79</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="5" t="n">
+        <v>375.93</v>
+      </c>
+      <c r="B85" s="6" t="n">
+        <v>-905.18</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B88" s="2" t="str">
+        <f aca="false">D6</f>
+        <v>#DDDDDD</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="5" t="n">
+        <v>170.41</v>
+      </c>
+      <c r="B91" s="6" t="n">
+        <v>-757.31</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="5" t="n">
+        <v>151.21</v>
+      </c>
+      <c r="B92" s="6" t="n">
+        <v>-683.77</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="B93" s="6" t="n">
+        <v>-710</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B96" s="2" t="str">
+        <f aca="false">D6</f>
+        <v>#DDDDDD</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B97" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="5" t="n">
+        <v>349.98</v>
+      </c>
+      <c r="B99" s="6" t="n">
+        <v>-641.01</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="5" t="n">
+        <v>341.16</v>
+      </c>
+      <c r="B100" s="6" t="n">
+        <v>-592.24</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="5" t="n">
+        <v>375.83</v>
+      </c>
+      <c r="B101" s="6" t="n">
+        <v>-560.8</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="5" t="n">
+        <v>403.74</v>
+      </c>
+      <c r="B102" s="6" t="n">
+        <v>-622.5</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B105" s="2" t="str">
+        <f aca="false">D6</f>
+        <v>#DDDDDD</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="5" t="n">
+        <v>386.45</v>
+      </c>
+      <c r="B108" s="6" t="n">
+        <v>-302.22</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="5" t="n">
+        <v>320.83</v>
+      </c>
+      <c r="B109" s="6" t="n">
+        <v>-236.99</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="5" t="n">
+        <v>373.09</v>
+      </c>
+      <c r="B110" s="6" t="n">
+        <v>-174.52</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="5" t="n">
+        <v>407.67</v>
+      </c>
+      <c r="B111" s="6" t="n">
+        <v>-241.31</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="5" t="n">
+        <v>537.33</v>
+      </c>
+      <c r="B112" s="6" t="n">
+        <v>-202.42</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="5" t="n">
+        <v>512.58</v>
+      </c>
+      <c r="B113" s="6" t="n">
+        <v>-287.29</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B116" s="2" t="str">
+        <f aca="false">D6</f>
+        <v>#DDDDDD</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="5" t="n">
+        <v>763.56</v>
+      </c>
+      <c r="B119" s="6" t="n">
+        <v>-408.67</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="5" t="n">
+        <v>794.44</v>
+      </c>
+      <c r="B120" s="6" t="n">
+        <v>-330.56</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="B121" s="6" t="n">
+        <v>-340</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="5" t="n">
+        <v>837.31</v>
+      </c>
+      <c r="B122" s="6" t="n">
+        <v>-402.13</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B125" s="2" t="n">
+        <f aca="false">D15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B126" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1515,7 +3582,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D392"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16.92"/>
@@ -1554,8 +3621,8 @@
         <v>8</v>
       </c>
       <c r="B3" s="2" t="str">
-        <f aca="false">D1</f>
-        <v>#555577</v>
+        <f aca="false">D2</f>
+        <v>#884433</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>9</v>
@@ -1593,20 +3660,3143 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
+      <c r="A6" s="9" t="n">
+        <v>382.4</v>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>-870.84</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
+      <c r="A7" s="9" t="n">
+        <v>276.24</v>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>-804.92</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6"/>
+      <c r="A8" s="9" t="n">
+        <v>117.14</v>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>-809.48</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6"/>
+      <c r="A9" s="9" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>-674.91</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="n">
+        <v>-104.27</v>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>-710.13</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="n">
+        <v>-182.92</v>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>-669.63</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="n">
+        <v>-169.42</v>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>-631.48</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="n">
+        <v>-95.47</v>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>-626.79</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="n">
+        <v>17.22</v>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>-542.86</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="n">
+        <v>-20.93</v>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>-480.64</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="n">
+        <v>-10.36</v>
+      </c>
+      <c r="B16" s="9" t="n">
+        <v>-457.17</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="n">
+        <v>113.48</v>
+      </c>
+      <c r="B17" s="9" t="n">
+        <v>-488.86</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="n">
+        <v>227.34</v>
+      </c>
+      <c r="B18" s="9" t="n">
+        <v>-448.36</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="n">
+        <v>235</v>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>-379.51</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="n">
+        <v>180.49</v>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>-375.31</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="n">
+        <v>107.59</v>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>-265.64</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="n">
+        <v>120</v>
+      </c>
+      <c r="B22" s="9" t="n">
+        <v>-240</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="n">
+        <v>160</v>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>-260</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="n">
+        <v>255.64</v>
+      </c>
+      <c r="B24" s="9" t="n">
+        <v>-238.87</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="n">
+        <v>314.35</v>
+      </c>
+      <c r="B25" s="9" t="n">
+        <v>-313.38</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="9" t="n">
+        <v>447.7</v>
+      </c>
+      <c r="B26" s="9" t="n">
+        <v>-358.52</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="9" t="n">
+        <v>544.51</v>
+      </c>
+      <c r="B27" s="9" t="n">
+        <v>-289.11</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="9" t="n">
+        <v>593.46</v>
+      </c>
+      <c r="B28" s="9" t="n">
+        <v>-369.86</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="9" t="n">
+        <v>737.42</v>
+      </c>
+      <c r="B29" s="9" t="n">
+        <v>-297.56</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="9" t="n">
+        <v>765.41</v>
+      </c>
+      <c r="B30" s="9" t="n">
+        <v>-312.43</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="9" t="n">
+        <v>728.38</v>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>-423.8</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="9" t="n">
+        <v>817.89</v>
+      </c>
+      <c r="B32" s="9" t="n">
+        <v>-424.09</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="9" t="n">
+        <v>872.4</v>
+      </c>
+      <c r="B33" s="9" t="n">
+        <v>-389.4</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="9" t="n">
+        <v>881.58</v>
+      </c>
+      <c r="B34" s="9" t="n">
+        <v>-484.21</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="9" t="n">
+        <v>856.62</v>
+      </c>
+      <c r="B35" s="9" t="n">
+        <v>-499.23</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="9" t="n">
+        <v>815.75</v>
+      </c>
+      <c r="B36" s="9" t="n">
+        <v>-572.68</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="9" t="n">
+        <v>905.68</v>
+      </c>
+      <c r="B37" s="9" t="n">
+        <v>-672.88</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="9" t="n">
+        <v>848.31</v>
+      </c>
+      <c r="B38" s="9" t="n">
+        <v>-735.71</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="9" t="n">
+        <v>805.23</v>
+      </c>
+      <c r="B39" s="9" t="n">
+        <v>-663.95</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="9" t="n">
+        <v>714.75</v>
+      </c>
+      <c r="B40" s="9" t="n">
+        <v>-716.37</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="9" t="n">
+        <v>685.47</v>
+      </c>
+      <c r="B41" s="9" t="n">
+        <v>-639.46</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="9" t="n">
+        <v>564.16</v>
+      </c>
+      <c r="B42" s="9" t="n">
+        <v>-666.84</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="9" t="n">
+        <v>528.05</v>
+      </c>
+      <c r="B43" s="9" t="n">
+        <v>-820.76</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B46" s="2" t="str">
+        <f aca="false">D6</f>
+        <v>#DDDDDD</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="9" t="n">
+        <v>160</v>
+      </c>
+      <c r="B49" s="9" t="n">
+        <v>-780</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="9" t="n">
+        <v>85.47</v>
+      </c>
+      <c r="B50" s="9" t="n">
+        <v>-672.21</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="9" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="B51" s="9" t="n">
+        <v>-571.39</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="9" t="n">
+        <v>218.73</v>
+      </c>
+      <c r="B52" s="9" t="n">
+        <v>-602.55</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="9" t="n">
+        <v>237.43</v>
+      </c>
+      <c r="B53" s="9" t="n">
+        <v>-675.78</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="9" t="n">
+        <v>260</v>
+      </c>
+      <c r="B54" s="9" t="n">
+        <v>-720</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B57" s="2" t="str">
+        <f aca="false">D6</f>
+        <v>#DDDDDD</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="9" t="n">
+        <v>299.34</v>
+      </c>
+      <c r="B60" s="9" t="n">
+        <v>-630.92</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="9" t="n">
+        <v>285.2</v>
+      </c>
+      <c r="B61" s="9" t="n">
+        <v>-526.07</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="9" t="n">
+        <v>374.73</v>
+      </c>
+      <c r="B62" s="9" t="n">
+        <v>-429.47</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="9" t="n">
+        <v>465.05</v>
+      </c>
+      <c r="B63" s="9" t="n">
+        <v>-466.38</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="9" t="n">
+        <v>443.46</v>
+      </c>
+      <c r="B64" s="9" t="n">
+        <v>-513.11</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="9" t="n">
+        <v>480</v>
+      </c>
+      <c r="B65" s="9" t="n">
+        <v>-580</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="9" t="n">
+        <v>371.99</v>
+      </c>
+      <c r="B66" s="9" t="n">
+        <v>-654.48</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B69" s="2" t="str">
+        <f aca="false">D6</f>
+        <v>#DDDDDD</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="9" t="n">
+        <v>712.39</v>
+      </c>
+      <c r="B72" s="9" t="n">
+        <v>-552.76</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="9" t="n">
+        <v>637.03</v>
+      </c>
+      <c r="B73" s="9" t="n">
+        <v>-508.36</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="9" t="n">
+        <v>659.42</v>
+      </c>
+      <c r="B74" s="9" t="n">
+        <v>-477.03</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="9" t="n">
+        <v>640</v>
+      </c>
+      <c r="B75" s="9" t="n">
+        <v>-420</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="9" t="n">
+        <v>695.6</v>
+      </c>
+      <c r="B76" s="9" t="n">
+        <v>-437.11</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="9" t="n">
+        <v>703.06</v>
+      </c>
+      <c r="B77" s="9" t="n">
+        <v>-497.54</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="9" t="n">
+        <v>749.32</v>
+      </c>
+      <c r="B78" s="9" t="n">
+        <v>-497.17</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B81" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="9" t="n">
+        <v>232.11</v>
+      </c>
+      <c r="B84" s="9" t="n">
+        <v>-712.79</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="9" t="n">
+        <v>204.37</v>
+      </c>
+      <c r="B85" s="9" t="n">
+        <v>-724.63</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="9" t="n">
+        <v>200</v>
+      </c>
+      <c r="B86" s="9" t="n">
+        <v>-680</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="9" t="n">
+        <v>121.61</v>
+      </c>
+      <c r="B87" s="9" t="n">
+        <v>-646.42</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="9" t="n">
+        <v>121.94</v>
+      </c>
+      <c r="B88" s="9" t="n">
+        <v>-598.39</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="9" t="n">
+        <v>205.18</v>
+      </c>
+      <c r="B89" s="9" t="n">
+        <v>-617.54</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B92" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B93" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="9" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="B95" s="9" t="n">
+        <v>-533.43</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="9" t="n">
+        <v>369.91</v>
+      </c>
+      <c r="B96" s="9" t="n">
+        <v>-475.09</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="9" t="n">
+        <v>427.13</v>
+      </c>
+      <c r="B97" s="9" t="n">
+        <v>-484.29</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="9" t="n">
+        <v>393.47</v>
+      </c>
+      <c r="B98" s="9" t="n">
+        <v>-548.47</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B101" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="9" t="n">
+        <v>416.59</v>
+      </c>
+      <c r="B104" s="9" t="n">
+        <v>-591.11</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="9" t="n">
+        <v>406.94</v>
+      </c>
+      <c r="B105" s="9" t="n">
+        <v>-566.42</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="9" t="n">
+        <v>443.52</v>
+      </c>
+      <c r="B106" s="9" t="n">
+        <v>-559.69</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="9" t="n">
+        <v>450.25</v>
+      </c>
+      <c r="B107" s="9" t="n">
+        <v>-569.11</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B110" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="9" t="n">
+        <v>679.45</v>
+      </c>
+      <c r="B113" s="9" t="n">
+        <v>-708.63</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="9" t="n">
+        <v>630.5</v>
+      </c>
+      <c r="B114" s="9" t="n">
+        <v>-709.22</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="9" t="n">
+        <v>573.25</v>
+      </c>
+      <c r="B115" s="9" t="n">
+        <v>-802.67</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="9" t="n">
+        <v>550.7</v>
+      </c>
+      <c r="B116" s="9" t="n">
+        <v>-783.09</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="9" t="n">
+        <v>592.53</v>
+      </c>
+      <c r="B117" s="9" t="n">
+        <v>-686.68</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="9" t="n">
+        <v>678.26</v>
+      </c>
+      <c r="B118" s="9" t="n">
+        <v>-671.25</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B121" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="9" t="n">
+        <v>284.97</v>
+      </c>
+      <c r="B124" s="9" t="n">
+        <v>-115.14</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="9" t="n">
+        <v>367.27</v>
+      </c>
+      <c r="B125" s="9" t="n">
+        <v>-118.98</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="9" t="n">
+        <v>386.24</v>
+      </c>
+      <c r="B126" s="9" t="n">
+        <v>-135.13</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="9" t="n">
+        <v>354.45</v>
+      </c>
+      <c r="B127" s="9" t="n">
+        <v>-145.64</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="9" t="n">
+        <v>402.7</v>
+      </c>
+      <c r="B128" s="9" t="n">
+        <v>-310.86</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="9" t="n">
+        <v>480.66</v>
+      </c>
+      <c r="B129" s="9" t="n">
+        <v>-302.43</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="9" t="n">
+        <v>442.55</v>
+      </c>
+      <c r="B130" s="9" t="n">
+        <v>-334.04</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B133" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B134" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="9" t="n">
+        <v>304.72</v>
+      </c>
+      <c r="B136" s="9" t="n">
+        <v>-221.27</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="9" t="n">
+        <v>241.65</v>
+      </c>
+      <c r="B137" s="9" t="n">
+        <v>-203.58</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="9" t="n">
+        <v>280</v>
+      </c>
+      <c r="B138" s="9" t="n">
+        <v>-160</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B141" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B142" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="9" t="n">
+        <v>210.88</v>
+      </c>
+      <c r="B144" s="9" t="n">
+        <v>-417.28</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="9" t="n">
+        <v>133.18</v>
+      </c>
+      <c r="B145" s="9" t="n">
+        <v>-461.19</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="9" t="n">
+        <v>145.85</v>
+      </c>
+      <c r="B146" s="9" t="n">
+        <v>-407.82</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="9" t="n">
+        <v>130.14</v>
+      </c>
+      <c r="B147" s="9" t="n">
+        <v>-354.27</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="9" t="n">
+        <v>153.62</v>
+      </c>
+      <c r="B148" s="9" t="n">
+        <v>-356.47</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="9" t="n">
+        <v>161.22</v>
+      </c>
+      <c r="B149" s="9" t="n">
+        <v>-386.7</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B152" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B153" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="9" t="n">
+        <v>289.72</v>
+      </c>
+      <c r="B155" s="9" t="n">
+        <v>-881.32</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="9" t="n">
+        <v>260</v>
+      </c>
+      <c r="B156" s="9" t="n">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="9" t="n">
+        <v>218.93</v>
+      </c>
+      <c r="B157" s="9" t="n">
+        <v>-874.32</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="9" t="n">
+        <v>223.23</v>
+      </c>
+      <c r="B158" s="9" t="n">
+        <v>-863.29</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B161" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B162" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="9" t="n">
+        <v>141.1</v>
+      </c>
+      <c r="B164" s="9" t="n">
+        <v>-836.88</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="9" t="n">
+        <v>73.19</v>
+      </c>
+      <c r="B165" s="9" t="n">
+        <v>-874.36</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="9" t="n">
+        <v>36.44</v>
+      </c>
+      <c r="B166" s="9" t="n">
+        <v>-855.62</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="9" t="n">
+        <v>94.61</v>
+      </c>
+      <c r="B167" s="9" t="n">
+        <v>-818.87</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B170" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B171" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="9" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="B173" s="9" t="n">
+        <v>-802.84</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="9" t="n">
+        <v>55.94</v>
+      </c>
+      <c r="B174" s="9" t="n">
+        <v>-822.44</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="9" t="n">
+        <v>-42.69</v>
+      </c>
+      <c r="B175" s="9" t="n">
+        <v>-721.1</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="9" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="B176" s="9" t="n">
+        <v>-695.46</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B179" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B180" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="9" t="n">
+        <v>-129.23</v>
+      </c>
+      <c r="B182" s="9" t="n">
+        <v>-736.31</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="9" t="n">
+        <v>-195.42</v>
+      </c>
+      <c r="B183" s="9" t="n">
+        <v>-749.38</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="9" t="n">
+        <v>-222.69</v>
+      </c>
+      <c r="B184" s="9" t="n">
+        <v>-693.98</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="9" t="n">
+        <v>-211.02</v>
+      </c>
+      <c r="B185" s="9" t="n">
+        <v>-683.23</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B188" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B189" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="9" t="n">
+        <v>-198.8</v>
+      </c>
+      <c r="B191" s="9" t="n">
+        <v>-656.11</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="9" t="n">
+        <v>-226.3</v>
+      </c>
+      <c r="B192" s="9" t="n">
+        <v>-646.19</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="9" t="n">
+        <v>-193.84</v>
+      </c>
+      <c r="B193" s="9" t="n">
+        <v>-593.87</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="9" t="n">
+        <v>-159.47</v>
+      </c>
+      <c r="B194" s="9" t="n">
+        <v>-596.54</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B197" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B198" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="9" t="n">
+        <v>-125.86</v>
+      </c>
+      <c r="B200" s="9" t="n">
+        <v>-541.55</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="9" t="n">
+        <v>-142.28</v>
+      </c>
+      <c r="B201" s="9" t="n">
+        <v>-528.18</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="9" t="n">
+        <v>-120</v>
+      </c>
+      <c r="B202" s="9" t="n">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="9" t="n">
+        <v>-100.66</v>
+      </c>
+      <c r="B203" s="9" t="n">
+        <v>-512.91</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B205" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B206" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B207" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="9" t="n">
+        <v>-87.29</v>
+      </c>
+      <c r="B209" s="9" t="n">
+        <v>-599.21</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="9" t="n">
+        <v>-110.2</v>
+      </c>
+      <c r="B210" s="9" t="n">
+        <v>-583.94</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="9" t="n">
+        <v>-26.57</v>
+      </c>
+      <c r="B211" s="9" t="n">
+        <v>-516.34</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="9" t="n">
+        <v>-12.82</v>
+      </c>
+      <c r="B212" s="9" t="n">
+        <v>-537.35</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B214" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B215" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B216" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="9" t="n">
+        <v>-146.86</v>
+      </c>
+      <c r="B218" s="9" t="n">
+        <v>-377.06</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="9" t="n">
+        <v>-165.06</v>
+      </c>
+      <c r="B219" s="9" t="n">
+        <v>-356.14</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="9" t="n">
+        <v>-150.54</v>
+      </c>
+      <c r="B220" s="9" t="n">
+        <v>-325.14</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="9" t="n">
+        <v>-123.03</v>
+      </c>
+      <c r="B221" s="9" t="n">
+        <v>-332.12</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B223" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A224" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B224" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B225" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A226" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A227" s="9" t="n">
+        <v>-55.04</v>
+      </c>
+      <c r="B227" s="9" t="n">
+        <v>-455.32</v>
+      </c>
+    </row>
+    <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A228" s="9" t="n">
+        <v>-79.25</v>
+      </c>
+      <c r="B228" s="9" t="n">
+        <v>-433.04</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A229" s="9" t="n">
+        <v>-63.75</v>
+      </c>
+      <c r="B229" s="9" t="n">
+        <v>-401.66</v>
+      </c>
+    </row>
+    <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A230" s="9" t="n">
+        <v>-50.78</v>
+      </c>
+      <c r="B230" s="9" t="n">
+        <v>-405.53</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A231" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B232" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A233" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B233" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A234" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B234" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A235" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A236" s="9" t="n">
+        <v>39.03</v>
+      </c>
+      <c r="B236" s="9" t="n">
+        <v>-387.98</v>
+      </c>
+    </row>
+    <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="9" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="B237" s="9" t="n">
+        <v>-351.51</v>
+      </c>
+    </row>
+    <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A238" s="9" t="n">
+        <v>51.92</v>
+      </c>
+      <c r="B238" s="9" t="n">
+        <v>-356.55</v>
+      </c>
+    </row>
+    <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A239" s="9" t="n">
+        <v>67.44</v>
+      </c>
+      <c r="B239" s="9" t="n">
+        <v>-382.74</v>
+      </c>
+    </row>
+    <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A240" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A241" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B241" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A242" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B242" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B243" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A244" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A245" s="9" t="n">
+        <v>-31.73</v>
+      </c>
+      <c r="B245" s="9" t="n">
+        <v>-262.42</v>
+      </c>
+    </row>
+    <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A246" s="9" t="n">
+        <v>-53.86</v>
+      </c>
+      <c r="B246" s="9" t="n">
+        <v>-251.35</v>
+      </c>
+    </row>
+    <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A247" s="9" t="n">
+        <v>-40</v>
+      </c>
+      <c r="B247" s="9" t="n">
+        <v>-230</v>
+      </c>
+    </row>
+    <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A248" s="9" t="n">
+        <v>-31.35</v>
+      </c>
+      <c r="B248" s="9" t="n">
+        <v>-229.78</v>
+      </c>
+    </row>
+    <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A249" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A250" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B250" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A251" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B251" s="10" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A252" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B252" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A253" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A254" s="9" t="n">
+        <v>85.6</v>
+      </c>
+      <c r="B254" s="9" t="n">
+        <v>-273.56</v>
+      </c>
+    </row>
+    <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A255" s="9" t="n">
+        <v>102.49</v>
+      </c>
+      <c r="B255" s="9" t="n">
+        <v>-243.65</v>
+      </c>
+    </row>
+    <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A256" s="9" t="n">
+        <v>40.91</v>
+      </c>
+      <c r="B256" s="9" t="n">
+        <v>-223.59</v>
+      </c>
+    </row>
+    <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A257" s="9" t="n">
+        <v>37.39</v>
+      </c>
+      <c r="B257" s="9" t="n">
+        <v>-263</v>
+      </c>
+    </row>
+    <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A258" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A259" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B259" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A260" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B260" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A261" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B261" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A262" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A263" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="B263" s="9" t="n">
+        <v>-140</v>
+      </c>
+    </row>
+    <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A264" s="9" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="B264" s="9" t="n">
+        <v>-156.73</v>
+      </c>
+    </row>
+    <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A265" s="9" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="B265" s="9" t="n">
+        <v>-131.4</v>
+      </c>
+    </row>
+    <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A266" s="9" t="n">
+        <v>62.73</v>
+      </c>
+      <c r="B266" s="9" t="n">
+        <v>-125.06</v>
+      </c>
+    </row>
+    <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A267" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A268" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B268" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A269" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B269" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A270" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B270" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A271" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A272" s="9" t="n">
+        <v>403.55</v>
+      </c>
+      <c r="B272" s="9" t="n">
+        <v>-168.38</v>
+      </c>
+    </row>
+    <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A273" s="9" t="n">
+        <v>503.98</v>
+      </c>
+      <c r="B273" s="9" t="n">
+        <v>-156.53</v>
+      </c>
+    </row>
+    <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A274" s="9" t="n">
+        <v>517.43</v>
+      </c>
+      <c r="B274" s="9" t="n">
+        <v>-188.66</v>
+      </c>
+    </row>
+    <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A275" s="9" t="n">
+        <v>429.06</v>
+      </c>
+      <c r="B275" s="9" t="n">
+        <v>-216.38</v>
+      </c>
+    </row>
+    <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A276" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A277" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B277" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A278" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B278" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A279" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B279" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A280" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A281" s="9" t="n">
+        <v>547.36</v>
+      </c>
+      <c r="B281" s="9" t="n">
+        <v>-126.92</v>
+      </c>
+    </row>
+    <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A282" s="9" t="n">
+        <v>614.68</v>
+      </c>
+      <c r="B282" s="9" t="n">
+        <v>-178.57</v>
+      </c>
+    </row>
+    <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A283" s="9" t="n">
+        <v>584.71</v>
+      </c>
+      <c r="B283" s="9" t="n">
+        <v>-220.07</v>
+      </c>
+    </row>
+    <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A284" s="9" t="n">
+        <v>543.2</v>
+      </c>
+      <c r="B284" s="9" t="n">
+        <v>-165.43</v>
+      </c>
+    </row>
+    <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A285" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B285" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A286" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B286" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A287" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B287" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A288" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B288" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A289" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A290" s="9" t="n">
+        <v>577.65</v>
+      </c>
+      <c r="B290" s="9" t="n">
+        <v>-242.87</v>
+      </c>
+    </row>
+    <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A291" s="9" t="n">
+        <v>650.64</v>
+      </c>
+      <c r="B291" s="9" t="n">
+        <v>-317.93</v>
+      </c>
+    </row>
+    <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A292" s="9" t="n">
+        <v>599.84</v>
+      </c>
+      <c r="B292" s="9" t="n">
+        <v>-336.69</v>
+      </c>
+    </row>
+    <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A293" s="9" t="n">
+        <v>567.58</v>
+      </c>
+      <c r="B293" s="9" t="n">
+        <v>-285.21</v>
+      </c>
+    </row>
+    <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A294" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A295" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B295" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A296" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B296" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A297" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B297" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A298" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B298" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A299" s="9" t="n">
+        <v>780</v>
+      </c>
+      <c r="B299" s="9" t="n">
+        <v>-290</v>
+      </c>
+    </row>
+    <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A300" s="9" t="n">
+        <v>846.36</v>
+      </c>
+      <c r="B300" s="9" t="n">
+        <v>-255.21</v>
+      </c>
+    </row>
+    <row r="301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A301" s="9" t="n">
+        <v>846.55</v>
+      </c>
+      <c r="B301" s="9" t="n">
+        <v>-285.24</v>
+      </c>
+    </row>
+    <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A302" s="9" t="n">
+        <v>795.6</v>
+      </c>
+      <c r="B302" s="9" t="n">
+        <v>-315.66</v>
+      </c>
+    </row>
+    <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A303" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A304" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B304" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A305" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B305" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A306" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B306" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A307" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B307" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A308" s="9" t="n">
+        <v>844.42</v>
+      </c>
+      <c r="B308" s="9" t="n">
+        <v>-326.85</v>
+      </c>
+    </row>
+    <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A309" s="9" t="n">
+        <v>863.36</v>
+      </c>
+      <c r="B309" s="9" t="n">
+        <v>-312.6</v>
+      </c>
+    </row>
+    <row r="310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A310" s="9" t="n">
+        <v>877.61</v>
+      </c>
+      <c r="B310" s="9" t="n">
+        <v>-338.91</v>
+      </c>
+    </row>
+    <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A311" s="9" t="n">
+        <v>854.75</v>
+      </c>
+      <c r="B311" s="9" t="n">
+        <v>-357.38</v>
+      </c>
+    </row>
+    <row r="312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A312" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A313" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B313" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A314" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B314" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A315" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B315" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A316" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B316" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A317" s="9" t="n">
+        <v>944.88</v>
+      </c>
+      <c r="B317" s="9" t="n">
+        <v>-228.2</v>
+      </c>
+    </row>
+    <row r="318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A318" s="9" t="n">
+        <v>973.07</v>
+      </c>
+      <c r="B318" s="9" t="n">
+        <v>-261.89</v>
+      </c>
+    </row>
+    <row r="319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A319" s="9" t="n">
+        <v>923.07</v>
+      </c>
+      <c r="B319" s="9" t="n">
+        <v>-281.39</v>
+      </c>
+    </row>
+    <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A320" s="9" t="n">
+        <v>912.96</v>
+      </c>
+      <c r="B320" s="9" t="n">
+        <v>-266.14</v>
+      </c>
+    </row>
+    <row r="321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A321" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B321" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A322" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B322" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A323" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B323" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A324" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B324" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A325" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B325" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A326" s="9" t="n">
+        <v>880</v>
+      </c>
+      <c r="B326" s="9" t="n">
+        <v>-360</v>
+      </c>
+    </row>
+    <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A327" s="9" t="n">
+        <v>948.21</v>
+      </c>
+      <c r="B327" s="9" t="n">
+        <v>-329.22</v>
+      </c>
+    </row>
+    <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A328" s="9" t="n">
+        <v>950.64</v>
+      </c>
+      <c r="B328" s="9" t="n">
+        <v>-352.62</v>
+      </c>
+    </row>
+    <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A329" s="9" t="n">
+        <v>899.17</v>
+      </c>
+      <c r="B329" s="9" t="n">
+        <v>-434.42</v>
+      </c>
+    </row>
+    <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A330" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B330" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A331" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B331" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A332" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B332" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="333" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A333" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B333" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A334" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B334" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A335" s="9" t="n">
+        <v>860</v>
+      </c>
+      <c r="B335" s="9" t="n">
+        <v>-570</v>
+      </c>
+    </row>
+    <row r="336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A336" s="9" t="n">
+        <v>874.54</v>
+      </c>
+      <c r="B336" s="9" t="n">
+        <v>-554.19</v>
+      </c>
+    </row>
+    <row r="337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A337" s="9" t="n">
+        <v>943.6</v>
+      </c>
+      <c r="B337" s="9" t="n">
+        <v>-608.38</v>
+      </c>
+    </row>
+    <row r="338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A338" s="9" t="n">
+        <v>915.13</v>
+      </c>
+      <c r="B338" s="9" t="n">
+        <v>-639.24</v>
+      </c>
+    </row>
+    <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A339" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B339" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A340" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B340" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A341" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B341" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A342" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B342" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A343" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B343" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A344" s="9" t="n">
+        <v>848.77</v>
+      </c>
+      <c r="B344" s="9" t="n">
+        <v>-751.95</v>
+      </c>
+    </row>
+    <row r="345" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A345" s="9" t="n">
+        <v>927.74</v>
+      </c>
+      <c r="B345" s="9" t="n">
+        <v>-723.19</v>
+      </c>
+    </row>
+    <row r="346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A346" s="9" t="n">
+        <v>953.97</v>
+      </c>
+      <c r="B346" s="9" t="n">
+        <v>-756.47</v>
+      </c>
+    </row>
+    <row r="347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A347" s="9" t="n">
+        <v>832.69</v>
+      </c>
+      <c r="B347" s="9" t="n">
+        <v>-800.75</v>
+      </c>
+    </row>
+    <row r="348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A348" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B348" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A349" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B349" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A350" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B350" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A351" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B351" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A352" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B352" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A353" s="9" t="n">
+        <v>895.02</v>
+      </c>
+      <c r="B353" s="9" t="n">
+        <v>-840.23</v>
+      </c>
+    </row>
+    <row r="354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A354" s="9" t="n">
+        <v>953.97</v>
+      </c>
+      <c r="B354" s="9" t="n">
+        <v>-807.23</v>
+      </c>
+    </row>
+    <row r="355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A355" s="9" t="n">
+        <v>962.71</v>
+      </c>
+      <c r="B355" s="9" t="n">
+        <v>-822.46</v>
+      </c>
+    </row>
+    <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A356" s="9" t="n">
+        <v>904.89</v>
+      </c>
+      <c r="B356" s="9" t="n">
+        <v>-853.77</v>
+      </c>
+    </row>
+    <row r="357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A357" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B357" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A358" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B358" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A359" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B359" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A360" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B360" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A361" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B361" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A362" s="9" t="n">
+        <v>765.33</v>
+      </c>
+      <c r="B362" s="9" t="n">
+        <v>-713.26</v>
+      </c>
+    </row>
+    <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A363" s="9" t="n">
+        <v>808.45</v>
+      </c>
+      <c r="B363" s="9" t="n">
+        <v>-699.63</v>
+      </c>
+    </row>
+    <row r="364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A364" s="9" t="n">
+        <v>814.15</v>
+      </c>
+      <c r="B364" s="9" t="n">
+        <v>-718.75</v>
+      </c>
+    </row>
+    <row r="365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A365" s="9" t="n">
+        <v>780</v>
+      </c>
+      <c r="B365" s="9" t="n">
+        <v>-740</v>
+      </c>
+    </row>
+    <row r="366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A366" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B366" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A367" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B367" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A368" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B368" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A369" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B369" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A370" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B370" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A371" s="9" t="n">
+        <v>674.2</v>
+      </c>
+      <c r="B371" s="9" t="n">
+        <v>-733.34</v>
+      </c>
+    </row>
+    <row r="372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A372" s="9" t="n">
+        <v>700.55</v>
+      </c>
+      <c r="B372" s="9" t="n">
+        <v>-722.98</v>
+      </c>
+    </row>
+    <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A373" s="9" t="n">
+        <v>748.52</v>
+      </c>
+      <c r="B373" s="9" t="n">
+        <v>-753.61</v>
+      </c>
+    </row>
+    <row r="374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A374" s="9" t="n">
+        <v>707.98</v>
+      </c>
+      <c r="B374" s="9" t="n">
+        <v>-775.46</v>
+      </c>
+    </row>
+    <row r="375" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A375" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B375" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A376" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B376" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A377" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B377" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="378" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A378" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B378" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A379" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B379" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="380" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A380" s="9" t="n">
+        <v>655.27</v>
+      </c>
+      <c r="B380" s="9" t="n">
+        <v>-815.04</v>
+      </c>
+    </row>
+    <row r="381" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A381" s="9" t="n">
+        <v>677.33</v>
+      </c>
+      <c r="B381" s="9" t="n">
+        <v>-830.49</v>
+      </c>
+    </row>
+    <row r="382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A382" s="9" t="n">
+        <v>640.1</v>
+      </c>
+      <c r="B382" s="9" t="n">
+        <v>-863.58</v>
+      </c>
+    </row>
+    <row r="383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A383" s="9" t="n">
+        <v>625.48</v>
+      </c>
+      <c r="B383" s="9" t="n">
+        <v>-842.07</v>
+      </c>
+    </row>
+    <row r="384" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A384" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B384" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A385" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B385" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A386" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B386" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="387" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A387" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B387" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A388" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B388" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="389" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A389" s="9" t="n">
+        <v>559.19</v>
+      </c>
+      <c r="B389" s="9" t="n">
+        <v>-843.32</v>
+      </c>
+    </row>
+    <row r="390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A390" s="9" t="n">
+        <v>575.88</v>
+      </c>
+      <c r="B390" s="9" t="n">
+        <v>-879.97</v>
+      </c>
+    </row>
+    <row r="391" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A391" s="9" t="n">
+        <v>427.34</v>
+      </c>
+      <c r="B391" s="9" t="n">
+        <v>-889.55</v>
+      </c>
+    </row>
+    <row r="392" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A392" s="9" t="n">
+        <v>424.05</v>
+      </c>
+      <c r="B392" s="9" t="n">
+        <v>-865.75</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1624,7 +6814,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D362"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16.92"/>
@@ -1663,8 +6853,8 @@
         <v>8</v>
       </c>
       <c r="B3" s="2" t="str">
-        <f aca="false">D1</f>
-        <v>#555577</v>
+        <f aca="false">D2</f>
+        <v>#884433</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>9</v>
@@ -1702,20 +6892,2830 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
+      <c r="A6" s="9" t="n">
+        <v>402.51</v>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>-792.72</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
+      <c r="A7" s="9" t="n">
+        <v>368.9</v>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>-716.66</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6"/>
+      <c r="A8" s="9" t="n">
+        <v>297.44</v>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>-730.1</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6"/>
+      <c r="A9" s="9" t="n">
+        <v>219.59</v>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>-567.99</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="n">
+        <v>125.54</v>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>-556.51</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="n">
+        <v>-34.93</v>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>-660.24</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="n">
+        <v>-57.06</v>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>-635.65</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="n">
+        <v>48.18</v>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>-576.14</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>-531.88</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="n">
+        <v>51.13</v>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>-505.82</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="n">
+        <v>61.46</v>
+      </c>
+      <c r="B16" s="9" t="n">
+        <v>-491.07</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="n">
+        <v>144.08</v>
+      </c>
+      <c r="B17" s="9" t="n">
+        <v>-517.13</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="n">
+        <v>211.94</v>
+      </c>
+      <c r="B18" s="9" t="n">
+        <v>-515.65</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="n">
+        <v>285.22</v>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>-438.45</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="n">
+        <v>291.07</v>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>-377.4</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="n">
+        <v>328</v>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>-357.85</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="n">
+        <v>485.92</v>
+      </c>
+      <c r="B22" s="9" t="n">
+        <v>-443.42</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="n">
+        <v>523.44</v>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>-386.25</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="n">
+        <v>593.46</v>
+      </c>
+      <c r="B24" s="9" t="n">
+        <v>-392.01</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="n">
+        <v>604.97</v>
+      </c>
+      <c r="B25" s="9" t="n">
+        <v>-529.64</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="9" t="n">
+        <v>745.76</v>
+      </c>
+      <c r="B26" s="9" t="n">
+        <v>-581.22</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="9" t="n">
+        <v>786.43</v>
+      </c>
+      <c r="B27" s="9" t="n">
+        <v>-558.93</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="9" t="n">
+        <v>801.29</v>
+      </c>
+      <c r="B28" s="9" t="n">
+        <v>-603.51</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="9" t="n">
+        <v>783.69</v>
+      </c>
+      <c r="B29" s="9" t="n">
+        <v>-637.14</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="9" t="n">
+        <v>730.9</v>
+      </c>
+      <c r="B30" s="9" t="n">
+        <v>-643</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="9" t="n">
+        <v>626.49</v>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>-594.12</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="9" t="n">
+        <v>511.12</v>
+      </c>
+      <c r="B32" s="9" t="n">
+        <v>-654.74</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="9" t="n">
+        <v>480.62</v>
+      </c>
+      <c r="B33" s="9" t="n">
+        <v>-783.42</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" s="2" t="str">
+        <f aca="false">D6</f>
+        <v>#DDDDDD</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="9" t="n">
+        <v>409.47</v>
+      </c>
+      <c r="B39" s="9" t="n">
+        <v>-723.24</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="9" t="n">
+        <v>365.88</v>
+      </c>
+      <c r="B40" s="9" t="n">
+        <v>-668.68</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="9" t="n">
+        <v>320</v>
+      </c>
+      <c r="B41" s="9" t="n">
+        <v>-680</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="9" t="n">
+        <v>254.01</v>
+      </c>
+      <c r="B42" s="9" t="n">
+        <v>-585.01</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="9" t="n">
+        <v>243.96</v>
+      </c>
+      <c r="B43" s="9" t="n">
+        <v>-523.57</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="9" t="n">
+        <v>344.54</v>
+      </c>
+      <c r="B44" s="9" t="n">
+        <v>-429.79</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="9" t="n">
+        <v>528.97</v>
+      </c>
+      <c r="B45" s="9" t="n">
+        <v>-487.4</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="9" t="n">
+        <v>543.32</v>
+      </c>
+      <c r="B46" s="9" t="n">
+        <v>-440.09</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="9" t="n">
+        <v>565.91</v>
+      </c>
+      <c r="B47" s="9" t="n">
+        <v>-448.86</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="9" t="n">
+        <v>557.14</v>
+      </c>
+      <c r="B48" s="9" t="n">
+        <v>-540.55</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="9" t="n">
+        <v>597.54</v>
+      </c>
+      <c r="B49" s="9" t="n">
+        <v>-552.51</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="9" t="n">
+        <v>580.8</v>
+      </c>
+      <c r="B50" s="9" t="n">
+        <v>-585.99</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="9" t="n">
+        <v>473.58</v>
+      </c>
+      <c r="B51" s="9" t="n">
+        <v>-645.29</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="9" t="n">
+        <v>460</v>
+      </c>
+      <c r="B52" s="9" t="n">
+        <v>-720</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B55" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="9" t="n">
+        <v>388.35</v>
+      </c>
+      <c r="B58" s="9" t="n">
+        <v>-540.35</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="9" t="n">
+        <v>363.51</v>
+      </c>
+      <c r="B59" s="9" t="n">
+        <v>-531.71</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="9" t="n">
+        <v>373.08</v>
+      </c>
+      <c r="B60" s="9" t="n">
+        <v>-504.55</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="9" t="n">
+        <v>396.84</v>
+      </c>
+      <c r="B61" s="9" t="n">
+        <v>-507.18</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B64" s="2" t="n">
+        <f aca="false">D11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B65" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="9" t="n">
+        <v>483.29</v>
+      </c>
+      <c r="B67" s="9" t="n">
+        <v>-527.31</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="9" t="n">
+        <v>506.04</v>
+      </c>
+      <c r="B68" s="9" t="n">
+        <v>-509.07</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="9" t="n">
+        <v>550.95</v>
+      </c>
+      <c r="B69" s="9" t="n">
+        <v>-582.22</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="9" t="n">
+        <v>496.04</v>
+      </c>
+      <c r="B70" s="9" t="n">
+        <v>-603.99</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B73" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="9" t="n">
+        <v>399.5</v>
+      </c>
+      <c r="B76" s="9" t="n">
+        <v>-647.08</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="9" t="n">
+        <v>442.86</v>
+      </c>
+      <c r="B77" s="9" t="n">
+        <v>-634.47</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="9" t="n">
+        <v>445.03</v>
+      </c>
+      <c r="B78" s="9" t="n">
+        <v>-683.54</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="9" t="n">
+        <v>412.51</v>
+      </c>
+      <c r="B79" s="9" t="n">
+        <v>-687.68</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B82" s="11" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B83" s="11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B84" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="13" t="n">
+        <v>478.33</v>
+      </c>
+      <c r="B85" s="13" t="n">
+        <v>-816.19</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="13" t="n">
+        <v>379.74</v>
+      </c>
+      <c r="B86" s="13" t="n">
+        <v>-857.11</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="13" t="n">
+        <v>331.01</v>
+      </c>
+      <c r="B87" s="13" t="n">
+        <v>-810.98</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B88" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B89" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B90" s="11" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B91" s="11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B92" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="13" t="n">
+        <v>64.93</v>
+      </c>
+      <c r="B93" s="13" t="n">
+        <v>-625.95</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="13" t="n">
+        <v>61.08</v>
+      </c>
+      <c r="B94" s="13" t="n">
+        <v>-684.56</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="13" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="B95" s="13" t="n">
+        <v>-653.76</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B96" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B97" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B98" s="11" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B99" s="11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B100" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="13" t="n">
+        <v>22.13</v>
+      </c>
+      <c r="B101" s="13" t="n">
+        <v>-510.63</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="B102" s="13" t="n">
+        <v>-480</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="13" t="n">
+        <v>35.93</v>
+      </c>
+      <c r="B103" s="13" t="n">
+        <v>-489.46</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B104" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B105" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B106" s="11" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B107" s="11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B108" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="13" t="n">
+        <v>147.22</v>
+      </c>
+      <c r="B109" s="13" t="n">
+        <v>-493.79</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="13" t="n">
+        <v>216.44</v>
+      </c>
+      <c r="B110" s="13" t="n">
+        <v>-462.94</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="13" t="n">
+        <v>210.11</v>
+      </c>
+      <c r="B111" s="13" t="n">
+        <v>-492.61</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B112" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B113" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B114" s="11" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B115" s="11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B116" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="13" t="n">
+        <v>183.61</v>
+      </c>
+      <c r="B117" s="13" t="n">
+        <v>-418.25</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="13" t="n">
+        <v>148.8</v>
+      </c>
+      <c r="B118" s="13" t="n">
+        <v>-439.21</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="13" t="n">
+        <v>155.92</v>
+      </c>
+      <c r="B119" s="13" t="n">
+        <v>-402.82</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B120" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B121" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B122" s="11" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B123" s="11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B124" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="13" t="n">
+        <v>486.6</v>
+      </c>
+      <c r="B125" s="13" t="n">
+        <v>-173.63</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="13" t="n">
+        <v>442.67</v>
+      </c>
+      <c r="B126" s="13" t="n">
+        <v>-192.57</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="13" t="n">
+        <v>438.64</v>
+      </c>
+      <c r="B127" s="13" t="n">
+        <v>-175.65</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B128" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B129" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B130" s="11" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B131" s="11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B132" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="13" t="n">
+        <v>487.2</v>
+      </c>
+      <c r="B133" s="13" t="n">
+        <v>-378.27</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="13" t="n">
+        <v>480.58</v>
+      </c>
+      <c r="B134" s="13" t="n">
+        <v>-413.41</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="13" t="n">
+        <v>378.21</v>
+      </c>
+      <c r="B135" s="13" t="n">
+        <v>-355.35</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B136" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B137" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B138" s="11" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B139" s="11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B140" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="13" t="n">
+        <v>606.89</v>
+      </c>
+      <c r="B141" s="13" t="n">
+        <v>-431.24</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="13" t="n">
+        <v>632.35</v>
+      </c>
+      <c r="B142" s="13" t="n">
+        <v>-449.57</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="13" t="n">
+        <v>612.49</v>
+      </c>
+      <c r="B143" s="13" t="n">
+        <v>-492.35</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B144" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B145" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B146" s="11" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B147" s="11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B148" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="13" t="n">
+        <v>896.6</v>
+      </c>
+      <c r="B149" s="13" t="n">
+        <v>-406.13</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="13" t="n">
+        <v>891.56</v>
+      </c>
+      <c r="B150" s="13" t="n">
+        <v>-374.63</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="13" t="n">
+        <v>928.95</v>
+      </c>
+      <c r="B151" s="13" t="n">
+        <v>-364.13</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B152" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B153" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B154" s="11" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B155" s="11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B156" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="13" t="n">
+        <v>776.36</v>
+      </c>
+      <c r="B157" s="13" t="n">
+        <v>-665.27</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="13" t="n">
+        <v>720</v>
+      </c>
+      <c r="B158" s="13" t="n">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="13" t="n">
+        <v>716.84</v>
+      </c>
+      <c r="B159" s="13" t="n">
+        <v>-666.12</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B162" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B163" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="9" t="n">
+        <v>369.56</v>
+      </c>
+      <c r="B165" s="9" t="n">
+        <v>-778.6</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="9" t="n">
+        <v>319.93</v>
+      </c>
+      <c r="B166" s="9" t="n">
+        <v>-786.96</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="9" t="n">
+        <v>316.37</v>
+      </c>
+      <c r="B167" s="9" t="n">
+        <v>-749.07</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="9" t="n">
+        <v>367.07</v>
+      </c>
+      <c r="B168" s="9" t="n">
+        <v>-745.34</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B171" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B172" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="9" t="n">
+        <v>293.8</v>
+      </c>
+      <c r="B174" s="9" t="n">
+        <v>-781.03</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="9" t="n">
+        <v>195.38</v>
+      </c>
+      <c r="B175" s="9" t="n">
+        <v>-788.23</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="9" t="n">
+        <v>188.52</v>
+      </c>
+      <c r="B176" s="9" t="n">
+        <v>-771.08</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="9" t="n">
+        <v>269.11</v>
+      </c>
+      <c r="B177" s="9" t="n">
+        <v>-733.02</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B180" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B181" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="9" t="n">
+        <v>206.17</v>
+      </c>
+      <c r="B183" s="9" t="n">
+        <v>-645.8</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="9" t="n">
+        <v>193.59</v>
+      </c>
+      <c r="B184" s="9" t="n">
+        <v>-666.49</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="9" t="n">
+        <v>140</v>
+      </c>
+      <c r="B185" s="9" t="n">
+        <v>-640</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="9" t="n">
+        <v>147.75</v>
+      </c>
+      <c r="B186" s="9" t="n">
+        <v>-618.63</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B189" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B190" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="9" t="n">
+        <v>132.34</v>
+      </c>
+      <c r="B192" s="9" t="n">
+        <v>-765.47</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="9" t="n">
+        <v>120.58</v>
+      </c>
+      <c r="B193" s="9" t="n">
+        <v>-785.75</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="9" t="n">
+        <v>61.76</v>
+      </c>
+      <c r="B194" s="9" t="n">
+        <v>-713.95</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="9" t="n">
+        <v>80.42</v>
+      </c>
+      <c r="B195" s="9" t="n">
+        <v>-694.48</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B198" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B199" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="9" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="B201" s="9" t="n">
+        <v>-827.52</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="9" t="n">
+        <v>114.76</v>
+      </c>
+      <c r="B202" s="9" t="n">
+        <v>-844.96</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="9" t="n">
+        <v>71.17</v>
+      </c>
+      <c r="B203" s="9" t="n">
+        <v>-865.75</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="9" t="n">
+        <v>53.73</v>
+      </c>
+      <c r="B204" s="9" t="n">
+        <v>-852.34</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B206" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B207" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B208" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="9" t="n">
+        <v>81.23</v>
+      </c>
+      <c r="B210" s="9" t="n">
+        <v>-793.65</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="9" t="n">
+        <v>54.74</v>
+      </c>
+      <c r="B211" s="9" t="n">
+        <v>-808.07</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="9" t="n">
+        <v>-22.05</v>
+      </c>
+      <c r="B212" s="9" t="n">
+        <v>-733.3</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="9" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="B213" s="9" t="n">
+        <v>-712.5</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B215" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B216" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B217" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="9" t="n">
+        <v>-80.79</v>
+      </c>
+      <c r="B219" s="9" t="n">
+        <v>-648.45</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="9" t="n">
+        <v>-65.08</v>
+      </c>
+      <c r="B220" s="9" t="n">
+        <v>-673.05</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="9" t="n">
+        <v>-101.99</v>
+      </c>
+      <c r="B221" s="9" t="n">
+        <v>-690.85</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="9" t="n">
+        <v>-149.1</v>
+      </c>
+      <c r="B222" s="9" t="n">
+        <v>-653.42</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A224" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B224" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B225" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A226" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B226" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A227" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A228" s="9" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="B228" s="9" t="n">
+        <v>-530.23</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A229" s="9" t="n">
+        <v>51.22</v>
+      </c>
+      <c r="B229" s="9" t="n">
+        <v>-536.72</v>
+      </c>
+    </row>
+    <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A230" s="9" t="n">
+        <v>38.81</v>
+      </c>
+      <c r="B230" s="9" t="n">
+        <v>-568.42</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A231" s="9" t="n">
+        <v>17.61</v>
+      </c>
+      <c r="B231" s="9" t="n">
+        <v>-569.37</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A233" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B233" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A234" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B234" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A235" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B235" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A236" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="9" t="n">
+        <v>271.41</v>
+      </c>
+      <c r="B237" s="9" t="n">
+        <v>-423.56</v>
+      </c>
+    </row>
+    <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A238" s="9" t="n">
+        <v>243.85</v>
+      </c>
+      <c r="B238" s="9" t="n">
+        <v>-440.05</v>
+      </c>
+    </row>
+    <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A239" s="9" t="n">
+        <v>240</v>
+      </c>
+      <c r="B239" s="9" t="n">
+        <v>-360</v>
+      </c>
+    </row>
+    <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A240" s="9" t="n">
+        <v>272.64</v>
+      </c>
+      <c r="B240" s="9" t="n">
+        <v>-345.78</v>
+      </c>
+    </row>
+    <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A241" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A242" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B242" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B243" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A244" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B244" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A245" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A246" s="9" t="n">
+        <v>273.63</v>
+      </c>
+      <c r="B246" s="9" t="n">
+        <v>-313.29</v>
+      </c>
+    </row>
+    <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A247" s="9" t="n">
+        <v>206.19</v>
+      </c>
+      <c r="B247" s="9" t="n">
+        <v>-355.87</v>
+      </c>
+    </row>
+    <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A248" s="9" t="n">
+        <v>141.45</v>
+      </c>
+      <c r="B248" s="9" t="n">
+        <v>-277.35</v>
+      </c>
+    </row>
+    <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A249" s="9" t="n">
+        <v>241.63</v>
+      </c>
+      <c r="B249" s="9" t="n">
+        <v>-265.29</v>
+      </c>
+    </row>
+    <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A250" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A251" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B251" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A252" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B252" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A253" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B253" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A254" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A255" s="9" t="n">
+        <v>305.15</v>
+      </c>
+      <c r="B255" s="9" t="n">
+        <v>-195.02</v>
+      </c>
+    </row>
+    <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A256" s="9" t="n">
+        <v>277.63</v>
+      </c>
+      <c r="B256" s="9" t="n">
+        <v>-186.34</v>
+      </c>
+    </row>
+    <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A257" s="9" t="n">
+        <v>302.16</v>
+      </c>
+      <c r="B257" s="9" t="n">
+        <v>-147.75</v>
+      </c>
+    </row>
+    <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A258" s="9" t="n">
+        <v>340.75</v>
+      </c>
+      <c r="B258" s="9" t="n">
+        <v>-147.45</v>
+      </c>
+    </row>
+    <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A259" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A260" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B260" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A261" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B261" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A262" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B262" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A263" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A264" s="9" t="n">
+        <v>558.34</v>
+      </c>
+      <c r="B264" s="9" t="n">
+        <v>-351.06</v>
+      </c>
+    </row>
+    <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A265" s="9" t="n">
+        <v>521.36</v>
+      </c>
+      <c r="B265" s="9" t="n">
+        <v>-369.34</v>
+      </c>
+    </row>
+    <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A266" s="9" t="n">
+        <v>499.22</v>
+      </c>
+      <c r="B266" s="9" t="n">
+        <v>-348.27</v>
+      </c>
+    </row>
+    <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A267" s="9" t="n">
+        <v>531.46</v>
+      </c>
+      <c r="B267" s="9" t="n">
+        <v>-314.52</v>
+      </c>
+    </row>
+    <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A268" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A269" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B269" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A270" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B270" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A271" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B271" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A272" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A273" s="9" t="n">
+        <v>698.03</v>
+      </c>
+      <c r="B273" s="9" t="n">
+        <v>-407.97</v>
+      </c>
+    </row>
+    <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A274" s="9" t="n">
+        <v>636.07</v>
+      </c>
+      <c r="B274" s="9" t="n">
+        <v>-374.68</v>
+      </c>
+    </row>
+    <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A275" s="9" t="n">
+        <v>717.95</v>
+      </c>
+      <c r="B275" s="9" t="n">
+        <v>-317.09</v>
+      </c>
+    </row>
+    <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A276" s="9" t="n">
+        <v>739.24</v>
+      </c>
+      <c r="B276" s="9" t="n">
+        <v>-325.83</v>
+      </c>
+    </row>
+    <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A277" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A278" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B278" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A279" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B279" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A280" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B280" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A281" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A282" s="9" t="n">
+        <v>824.42</v>
+      </c>
+      <c r="B282" s="9" t="n">
+        <v>-483.65</v>
+      </c>
+    </row>
+    <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A283" s="9" t="n">
+        <v>727.29</v>
+      </c>
+      <c r="B283" s="9" t="n">
+        <v>-480.36</v>
+      </c>
+    </row>
+    <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A284" s="9" t="n">
+        <v>728.56</v>
+      </c>
+      <c r="B284" s="9" t="n">
+        <v>-451.28</v>
+      </c>
+    </row>
+    <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A285" s="9" t="n">
+        <v>841.62</v>
+      </c>
+      <c r="B285" s="9" t="n">
+        <v>-445.71</v>
+      </c>
+    </row>
+    <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A286" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B286" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A287" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B287" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A288" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B288" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A289" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B289" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A290" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B290" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A291" s="9" t="n">
+        <v>802.28</v>
+      </c>
+      <c r="B291" s="9" t="n">
+        <v>-539.81</v>
+      </c>
+    </row>
+    <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A292" s="9" t="n">
+        <v>755.91</v>
+      </c>
+      <c r="B292" s="9" t="n">
+        <v>-543.94</v>
+      </c>
+    </row>
+    <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A293" s="9" t="n">
+        <v>770.45</v>
+      </c>
+      <c r="B293" s="9" t="n">
+        <v>-511.32</v>
+      </c>
+    </row>
+    <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A294" s="9" t="n">
+        <v>807.98</v>
+      </c>
+      <c r="B294" s="9" t="n">
+        <v>-514.07</v>
+      </c>
+    </row>
+    <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A295" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B295" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A296" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B296" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A297" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B297" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A298" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B298" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A299" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B299" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A300" s="9" t="n">
+        <v>885.09</v>
+      </c>
+      <c r="B300" s="9" t="n">
+        <v>-673.05</v>
+      </c>
+    </row>
+    <row r="301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A301" s="9" t="n">
+        <v>851.98</v>
+      </c>
+      <c r="B301" s="9" t="n">
+        <v>-705.41</v>
+      </c>
+    </row>
+    <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A302" s="9" t="n">
+        <v>806.91</v>
+      </c>
+      <c r="B302" s="9" t="n">
+        <v>-639.68</v>
+      </c>
+    </row>
+    <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A303" s="9" t="n">
+        <v>826.33</v>
+      </c>
+      <c r="B303" s="9" t="n">
+        <v>-617.27</v>
+      </c>
+    </row>
+    <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A304" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B304" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A305" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B305" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A306" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B306" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A307" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B307" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A308" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B308" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A309" s="9" t="n">
+        <v>903.71</v>
+      </c>
+      <c r="B309" s="9" t="n">
+        <v>-737.55</v>
+      </c>
+    </row>
+    <row r="310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A310" s="9" t="n">
+        <v>909.11</v>
+      </c>
+      <c r="B310" s="9" t="n">
+        <v>-755.68</v>
+      </c>
+    </row>
+    <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A311" s="9" t="n">
+        <v>871.33</v>
+      </c>
+      <c r="B311" s="9" t="n">
+        <v>-776.18</v>
+      </c>
+    </row>
+    <row r="312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A312" s="9" t="n">
+        <v>866.37</v>
+      </c>
+      <c r="B312" s="9" t="n">
+        <v>-752.22</v>
+      </c>
+    </row>
+    <row r="313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A313" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B313" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A314" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B314" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A315" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B315" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A316" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B316" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A317" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B317" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A318" s="9" t="n">
+        <v>635.88</v>
+      </c>
+      <c r="B318" s="9" t="n">
+        <v>-617.74</v>
+      </c>
+    </row>
+    <row r="319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A319" s="9" t="n">
+        <v>647.59</v>
+      </c>
+      <c r="B319" s="9" t="n">
+        <v>-638.69</v>
+      </c>
+    </row>
+    <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A320" s="9" t="n">
+        <v>573.04</v>
+      </c>
+      <c r="B320" s="9" t="n">
+        <v>-663.64</v>
+      </c>
+    </row>
+    <row r="321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A321" s="9" t="n">
+        <v>569.66</v>
+      </c>
+      <c r="B321" s="9" t="n">
+        <v>-641.46</v>
+      </c>
+    </row>
+    <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A322" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B322" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A323" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B323" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A324" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B324" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A325" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B325" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A326" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B326" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A327" s="9" t="n">
+        <v>594.61</v>
+      </c>
+      <c r="B327" s="9" t="n">
+        <v>-698.75</v>
+      </c>
+    </row>
+    <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A328" s="9" t="n">
+        <v>620</v>
+      </c>
+      <c r="B328" s="9" t="n">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A329" s="9" t="n">
+        <v>585.67</v>
+      </c>
+      <c r="B329" s="9" t="n">
+        <v>-766.83</v>
+      </c>
+    </row>
+    <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A330" s="9" t="n">
+        <v>568.42</v>
+      </c>
+      <c r="B330" s="9" t="n">
+        <v>-754.82</v>
+      </c>
+    </row>
+    <row r="331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A331" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B331" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A332" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B332" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="333" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A333" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B333" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A334" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B334" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A335" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B335" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A336" s="9" t="n">
+        <v>513.59</v>
+      </c>
+      <c r="B336" s="9" t="n">
+        <v>-791.48</v>
+      </c>
+    </row>
+    <row r="337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A337" s="9" t="n">
+        <v>494.49</v>
+      </c>
+      <c r="B337" s="9" t="n">
+        <v>-791.48</v>
+      </c>
+    </row>
+    <row r="338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A338" s="9" t="n">
+        <v>527.45</v>
+      </c>
+      <c r="B338" s="9" t="n">
+        <v>-667.03</v>
+      </c>
+    </row>
+    <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A339" s="9" t="n">
+        <v>551.48</v>
+      </c>
+      <c r="B339" s="9" t="n">
+        <v>-673.19</v>
+      </c>
+    </row>
+    <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A340" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B340" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A341" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B341" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A342" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B342" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A343" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B343" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A344" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B344" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="345" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A345" s="9" t="n">
+        <v>556.55</v>
+      </c>
+      <c r="B345" s="9" t="n">
+        <v>-849.76</v>
+      </c>
+    </row>
+    <row r="346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A346" s="9" t="n">
+        <v>557.62</v>
+      </c>
+      <c r="B346" s="9" t="n">
+        <v>-873.71</v>
+      </c>
+    </row>
+    <row r="347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A347" s="9" t="n">
+        <v>474.15</v>
+      </c>
+      <c r="B347" s="9" t="n">
+        <v>-876.94</v>
+      </c>
+    </row>
+    <row r="348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A348" s="9" t="n">
+        <v>476.3</v>
+      </c>
+      <c r="B348" s="9" t="n">
+        <v>-857.31</v>
+      </c>
+    </row>
+    <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A349" s="2"/>
+      <c r="B349" s="2"/>
+    </row>
+    <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A350" s="2"/>
+      <c r="B350" s="4"/>
+    </row>
+    <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A351" s="2"/>
+      <c r="B351" s="2"/>
+    </row>
+    <row r="352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A352" s="2"/>
+      <c r="B352" s="2"/>
+    </row>
+    <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A353" s="2"/>
+      <c r="B353" s="2"/>
+    </row>
+    <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A358" s="2"/>
+      <c r="B358" s="2"/>
+    </row>
+    <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A359" s="2"/>
+      <c r="B359" s="4"/>
+    </row>
+    <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A360" s="2"/>
+      <c r="B360" s="2"/>
+    </row>
+    <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A361" s="2"/>
+      <c r="B361" s="2"/>
+    </row>
+    <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A362" s="2"/>
+      <c r="B362" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1733,7 +9733,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D140"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16.92"/>
@@ -1772,8 +9772,8 @@
         <v>8</v>
       </c>
       <c r="B3" s="2" t="str">
-        <f aca="false">D1</f>
-        <v>#555577</v>
+        <f aca="false">D2</f>
+        <v>#884433</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>9</v>
@@ -1811,22 +9811,1125 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
+      <c r="A6" s="9" t="n">
+        <v>440</v>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>-820</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
+      <c r="A7" s="9" t="n">
+        <v>392.15</v>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>-843.93</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6"/>
+      <c r="A8" s="9" t="n">
+        <v>362.79</v>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>-820.65</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6"/>
+      <c r="A9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="n">
+        <v>726.43</v>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>-320.89</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="n">
+        <v>697.61</v>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>-394.69</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="n">
+        <v>663.17</v>
+      </c>
+      <c r="B16" s="9" t="n">
+        <v>-376.06</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="n">
+        <v>828.95</v>
+      </c>
+      <c r="B22" s="9" t="n">
+        <v>-632.82</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="n">
+        <v>872.19</v>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>-677.44</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="n">
+        <v>852.64</v>
+      </c>
+      <c r="B24" s="9" t="n">
+        <v>-700.3</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="9" t="n">
+        <v>-34.68</v>
+      </c>
+      <c r="B30" s="9" t="n">
+        <v>-624.78</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="9" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>-602.66</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="9" t="n">
+        <v>-26.63</v>
+      </c>
+      <c r="B32" s="9" t="n">
+        <v>-646.57</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="9" t="n">
+        <v>278.19</v>
+      </c>
+      <c r="B38" s="9" t="n">
+        <v>-745.63</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="9" t="n">
+        <v>291.25</v>
+      </c>
+      <c r="B39" s="9" t="n">
+        <v>-767.5</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="9" t="n">
+        <v>228.8</v>
+      </c>
+      <c r="B40" s="9" t="n">
+        <v>-776.32</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="9" t="n">
+        <v>219.28</v>
+      </c>
+      <c r="B41" s="9" t="n">
+        <v>-763.62</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="9" t="n">
+        <v>265.85</v>
+      </c>
+      <c r="B47" s="9" t="n">
+        <v>-636.61</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="9" t="n">
+        <v>279.96</v>
+      </c>
+      <c r="B48" s="9" t="n">
+        <v>-631.67</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="9" t="n">
+        <v>303.59</v>
+      </c>
+      <c r="B49" s="9" t="n">
+        <v>-712.82</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="9" t="n">
+        <v>324.06</v>
+      </c>
+      <c r="B50" s="9" t="n">
+        <v>-704.7</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B53" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="9" t="n">
+        <v>121.23</v>
+      </c>
+      <c r="B56" s="9" t="n">
+        <v>-526.94</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="9" t="n">
+        <v>94.62</v>
+      </c>
+      <c r="B57" s="9" t="n">
+        <v>-572.5</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="9" t="n">
+        <v>72.85</v>
+      </c>
+      <c r="B58" s="9" t="n">
+        <v>-568.07</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="9" t="n">
+        <v>87.76</v>
+      </c>
+      <c r="B59" s="9" t="n">
+        <v>-528.15</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B62" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="9" t="n">
+        <v>311.54</v>
+      </c>
+      <c r="B65" s="9" t="n">
+        <v>-453.56</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="9" t="n">
+        <v>255.09</v>
+      </c>
+      <c r="B66" s="9" t="n">
+        <v>-507.59</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="9" t="n">
+        <v>242.99</v>
+      </c>
+      <c r="B67" s="9" t="n">
+        <v>-490.66</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="9" t="n">
+        <v>284.12</v>
+      </c>
+      <c r="B68" s="9" t="n">
+        <v>-454.37</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B71" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="9" t="n">
+        <v>362.74</v>
+      </c>
+      <c r="B74" s="9" t="n">
+        <v>-397.52</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="9" t="n">
+        <v>311.54</v>
+      </c>
+      <c r="B75" s="9" t="n">
+        <v>-438.24</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="9" t="n">
+        <v>303.47</v>
+      </c>
+      <c r="B76" s="9" t="n">
+        <v>-390.66</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="9" t="n">
+        <v>320.01</v>
+      </c>
+      <c r="B77" s="9" t="n">
+        <v>-375.74</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B80" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="9" t="n">
+        <v>257.11</v>
+      </c>
+      <c r="B83" s="9" t="n">
+        <v>-309.22</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="9" t="n">
+        <v>203.08</v>
+      </c>
+      <c r="B84" s="9" t="n">
+        <v>-345.1</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="9" t="n">
+        <v>178.48</v>
+      </c>
+      <c r="B85" s="9" t="n">
+        <v>-296.31</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="9" t="n">
+        <v>240.98</v>
+      </c>
+      <c r="B86" s="9" t="n">
+        <v>-276.15</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B89" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="9" t="n">
+        <v>474.95</v>
+      </c>
+      <c r="B92" s="9" t="n">
+        <v>-725.02</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="9" t="n">
+        <v>465.89</v>
+      </c>
+      <c r="B93" s="9" t="n">
+        <v>-765.52</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="9" t="n">
+        <v>407</v>
+      </c>
+      <c r="B94" s="9" t="n">
+        <v>-777.78</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="9" t="n">
+        <v>406.47</v>
+      </c>
+      <c r="B95" s="9" t="n">
+        <v>-743.67</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B98" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B99" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="9" t="n">
+        <v>516.73</v>
+      </c>
+      <c r="B101" s="9" t="n">
+        <v>-533.91</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="9" t="n">
+        <v>538.32</v>
+      </c>
+      <c r="B102" s="9" t="n">
+        <v>-577.1</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="9" t="n">
+        <v>503.94</v>
+      </c>
+      <c r="B103" s="9" t="n">
+        <v>-590.17</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="9" t="n">
+        <v>496.27</v>
+      </c>
+      <c r="B104" s="9" t="n">
+        <v>-548.12</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B107" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="9" t="n">
+        <v>493.71</v>
+      </c>
+      <c r="B110" s="9" t="n">
+        <v>-446.7</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="9" t="n">
+        <v>520</v>
+      </c>
+      <c r="B111" s="9" t="n">
+        <v>-460</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="9" t="n">
+        <v>549.11</v>
+      </c>
+      <c r="B112" s="9" t="n">
+        <v>-394.14</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="9" t="n">
+        <v>567.58</v>
+      </c>
+      <c r="B113" s="9" t="n">
+        <v>-404.65</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B116" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="9" t="n">
+        <v>564.74</v>
+      </c>
+      <c r="B119" s="9" t="n">
+        <v>-439.88</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="9" t="n">
+        <v>566.73</v>
+      </c>
+      <c r="B120" s="9" t="n">
+        <v>-521.13</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="9" t="n">
+        <v>592.87</v>
+      </c>
+      <c r="B121" s="9" t="n">
+        <v>-524.54</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="9" t="n">
+        <v>582.35</v>
+      </c>
+      <c r="B122" s="9" t="n">
+        <v>-431.35</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B125" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B126" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="9" t="n">
+        <v>623.49</v>
+      </c>
+      <c r="B128" s="9" t="n">
+        <v>-558.29</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="9" t="n">
+        <v>751.81</v>
+      </c>
+      <c r="B129" s="9" t="n">
+        <v>-600.77</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="9" t="n">
+        <v>740.25</v>
+      </c>
+      <c r="B130" s="9" t="n">
+        <v>-629.38</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="9" t="n">
+        <v>611.06</v>
+      </c>
+      <c r="B131" s="9" t="n">
+        <v>-574.18</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B134" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>#884433</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B135" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="9" t="n">
+        <v>759.61</v>
+      </c>
+      <c r="B137" s="9" t="n">
+        <v>-454.25</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="9" t="n">
+        <v>824.06</v>
+      </c>
+      <c r="B138" s="9" t="n">
+        <v>-456.27</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="9" t="n">
+        <v>823.19</v>
+      </c>
+      <c r="B139" s="9" t="n">
+        <v>-477.08</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="9" t="n">
+        <v>750.94</v>
+      </c>
+      <c r="B140" s="9" t="n">
+        <v>-479.97</v>
+      </c>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Página &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -7320,7 +16423,7 @@
       <c r="B73" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F73" s="7"/>
+      <c r="F73" s="2"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
